--- a/nhapcongviehangthang/cvthang4.xlsx
+++ b/nhapcongviehangthang/cvthang4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/nhapcongviehangthang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8841FFA-5C4E-5E49-85FE-E69DABEC7333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0113CC3-8FF0-A048-967F-7462BCE9E4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>Trần Diệp Mỹ Dung</t>
   </si>
   <si>
-    <t>H Hồng</t>
-  </si>
-  <si>
     <t>Đoàn Minh Tâm</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>Báo cáo</t>
+  </si>
+  <si>
+    <t>H' Hồng</t>
   </si>
 </sst>
 </file>
@@ -540,16 +540,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
@@ -560,10 +560,10 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="6">
         <v>46114</v>
@@ -573,15 +573,15 @@
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="19" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -660,7 +660,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -668,7 +668,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -676,7 +676,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -684,7 +684,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -692,17 +692,17 @@
         <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/nhapcongviehangthang/cvthang4.xlsx
+++ b/nhapcongviehangthang/cvthang4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/nhapcongviehangthang/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0113CC3-8FF0-A048-967F-7462BCE9E4E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD81E996-3D65-354C-A9E1-340B266DA822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>Lĩnh vực lớn</t>
   </si>
@@ -92,9 +92,6 @@
     <t>Châu Yến Phi</t>
   </si>
   <si>
-    <t>Báo cáo Tháng Thanh niên</t>
-  </si>
-  <si>
     <t xml:space="preserve">  </t>
   </si>
   <si>
@@ -110,18 +107,24 @@
     <t>Cán bộ phụ trách</t>
   </si>
   <si>
-    <t>Báo cáo</t>
-  </si>
-  <si>
     <t>H' Hồng</t>
+  </si>
+  <si>
+    <t>Kế hoạch phát động thi đua phong trào thi đua thực
+hiện thắng lợi nhiệm vụ phát triển kinh tế - xã hội, bảo
+đảm quốc phòng - an ninh năm 2026</t>
+  </si>
+  <si>
+    <t>Phan Xuân Tấn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -191,21 +194,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,81 +541,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="22.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="29.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="15" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" style="5" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="25" style="2" customWidth="1"/>
     <col min="10" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:9" s="8" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+      <c r="A2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="13">
+        <v>46091</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="H2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9" ht="19" x14ac:dyDescent="0.2">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="6">
-        <v>46114</v>
-      </c>
-      <c r="F2" s="6">
-        <v>46117</v>
-      </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="19" x14ac:dyDescent="0.2">
-      <c r="B8" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -660,7 +939,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">

--- a/nhapcongviehangthang/cvthang4.xlsx
+++ b/nhapcongviehangthang/cvthang4.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\THEO DÕI CV TINH ĐOÀN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pc/Desktop/quanlycongviectd/nhapcongviehangthang/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889FEC9B-F3EE-434C-ABEC-AB14F75FFB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8925"/>
+    <workbookView xWindow="1740" yWindow="600" windowWidth="21700" windowHeight="15080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapLieu" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="DanhMuc" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -578,7 +591,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
@@ -653,7 +666,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -704,12 +717,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -722,13 +729,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -981,12 +988,330 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -999,9 +1324,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1012,362 +1334,137 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1669,2320 +1766,2320 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" style="109" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" style="110" customWidth="1"/>
-    <col min="3" max="3" width="56.28515625" style="108" customWidth="1"/>
-    <col min="4" max="4" width="20.140625" style="105" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="107" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="131" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" style="106" customWidth="1"/>
-    <col min="8" max="8" width="22.28515625" style="105" customWidth="1"/>
-    <col min="9" max="9" width="25" style="105" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="103"/>
+    <col min="1" max="1" width="36.83203125" style="73" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" style="74" customWidth="1"/>
+    <col min="3" max="3" width="56.33203125" style="72" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="69" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="71" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="91" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" style="70" customWidth="1"/>
+    <col min="8" max="8" width="22.33203125" style="69" customWidth="1"/>
+    <col min="9" max="9" width="25" style="69" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="68"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="94" t="s">
+    <row r="1" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="94" t="s">
+      <c r="B1" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="111" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="94" t="s">
+      <c r="D1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="E1" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="F1" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="95" t="s">
+      <c r="G1" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="94" t="s">
+      <c r="H1" s="61" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="94" t="s">
+      <c r="I1" s="61" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:9" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="97" t="s">
+    <row r="2" spans="1:9" s="129" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="113" t="str">
+      <c r="C2" s="126" t="str">
         <f>Sheet1!F5</f>
         <v>Kế hoạch thực hiện Nghị Quyết 59 của Bộ Chính trị</v>
       </c>
-      <c r="D2" s="98"/>
-      <c r="E2" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F2" s="100">
+      <c r="D2" s="76"/>
+      <c r="E2" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F2" s="127">
         <v>46122</v>
       </c>
-      <c r="G2" s="99"/>
-      <c r="H2" s="98" t="s">
+      <c r="G2" s="128"/>
+      <c r="H2" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="98" t="s">
+      <c r="I2" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="97" t="s">
+    <row r="3" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="112" t="s">
+      <c r="B3" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="113" t="str">
+      <c r="C3" s="126" t="str">
         <f>Sheet1!F6</f>
         <v>Báo cáo công tác Đoàn tháng 4</v>
       </c>
-      <c r="D3" s="101"/>
-      <c r="E3" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F3" s="100">
+      <c r="D3" s="130"/>
+      <c r="E3" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F3" s="127">
         <f>Sheet1!I6</f>
         <v>46127</v>
       </c>
-      <c r="G3" s="102"/>
-      <c r="H3" s="98" t="s">
+      <c r="G3" s="131"/>
+      <c r="H3" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="I3" s="98" t="s">
+      <c r="I3" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="97" t="s">
+    <row r="4" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="112" t="s">
+      <c r="B4" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="113" t="str">
+      <c r="C4" s="126" t="str">
         <f>Sheet1!F7</f>
         <v>Hướng dẫn xử lý văn bản bí mật nhà nước</v>
       </c>
-      <c r="D4" s="101"/>
-      <c r="E4" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F4" s="100">
+      <c r="D4" s="130"/>
+      <c r="E4" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F4" s="127">
         <f>Sheet1!I7</f>
         <v>46122</v>
       </c>
-      <c r="G4" s="102"/>
-      <c r="H4" s="98" t="s">
+      <c r="G4" s="131"/>
+      <c r="H4" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="98" t="s">
+      <c r="I4" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="97" t="s">
+    <row r="5" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="112" t="s">
+      <c r="B5" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="113" t="str">
+      <c r="C5" s="126" t="str">
         <f>Sheet1!F8</f>
         <v>Báo cáo điều tra cơ sở hành chính sự nghiệp năm 2026</v>
       </c>
-      <c r="D5" s="101"/>
-      <c r="E5" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F5" s="100">
+      <c r="D5" s="130"/>
+      <c r="E5" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F5" s="127">
         <f>Sheet1!I8</f>
         <v>46122</v>
       </c>
-      <c r="G5" s="102"/>
-      <c r="H5" s="98" t="s">
+      <c r="G5" s="131"/>
+      <c r="H5" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="I5" s="98" t="s">
+      <c r="I5" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="97" t="s">
+    <row r="6" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="112" t="s">
+      <c r="B6" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="113" t="str">
+      <c r="C6" s="126" t="str">
         <f>Sheet1!F9</f>
         <v>Tham mưu lịch công tác Tháng và Tuần của Thường trực</v>
       </c>
-      <c r="D6" s="101"/>
-      <c r="E6" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F6" s="100">
+      <c r="D6" s="130"/>
+      <c r="E6" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F6" s="127">
         <v>46142</v>
       </c>
-      <c r="G6" s="102"/>
-      <c r="H6" s="98" t="s">
+      <c r="G6" s="131"/>
+      <c r="H6" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="I6" s="98" t="s">
+      <c r="I6" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="97" t="s">
+    <row r="7" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="112" t="s">
+      <c r="B7" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="113" t="str">
+      <c r="C7" s="126" t="str">
         <f>Sheet1!F10</f>
         <v>Thông báo kết quả giao ban tháng 4</v>
       </c>
-      <c r="D7" s="101"/>
-      <c r="E7" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F7" s="100">
+      <c r="D7" s="130"/>
+      <c r="E7" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F7" s="127">
         <v>46122</v>
       </c>
-      <c r="G7" s="102"/>
-      <c r="H7" s="98" t="s">
+      <c r="G7" s="131"/>
+      <c r="H7" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="98" t="s">
+      <c r="I7" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="97" t="s">
+    <row r="8" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="112" t="s">
+      <c r="B8" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="113" t="str">
+      <c r="C8" s="126" t="str">
         <f>Sheet1!F11</f>
         <v>Tham mưu tài liệu họp Ban Thường vụ Tỉnh đoàn tháng 4</v>
       </c>
-      <c r="D8" s="101"/>
-      <c r="E8" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F8" s="100">
+      <c r="D8" s="130"/>
+      <c r="E8" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F8" s="127">
         <f>Sheet1!I11</f>
         <v>46127</v>
       </c>
-      <c r="G8" s="102"/>
-      <c r="H8" s="98" t="s">
+      <c r="G8" s="131"/>
+      <c r="H8" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="98" t="s">
+      <c r="I8" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="97" t="s">
+    <row r="9" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="112" t="s">
+      <c r="B9" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="113" t="str">
+      <c r="C9" s="126" t="str">
         <f>Sheet1!F12</f>
         <v>Rà soát điều chỉnh Quy chế thi chi tiêu nội bộ tại Ban Công tác Đoàn và TTN</v>
       </c>
-      <c r="D9" s="101"/>
-      <c r="E9" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F9" s="100">
+      <c r="D9" s="130"/>
+      <c r="E9" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F9" s="127">
         <v>46127</v>
       </c>
-      <c r="G9" s="102"/>
-      <c r="H9" s="98" t="s">
+      <c r="G9" s="131"/>
+      <c r="H9" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="I9" s="98" t="s">
+      <c r="I9" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="97" t="s">
+    <row r="10" spans="1:9" s="132" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A10" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="113" t="str">
+      <c r="C10" s="126" t="str">
         <f>Sheet1!F13</f>
         <v>Báo cáo các nội dung liên quan phục vụ làm việc với Đoàn kiểm tra của Bộ Chính trị, Ban Bí thư</v>
       </c>
-      <c r="D10" s="101"/>
-      <c r="E10" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F10" s="100">
+      <c r="D10" s="130"/>
+      <c r="E10" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F10" s="127">
         <f>Sheet1!I13</f>
         <v>46120</v>
       </c>
-      <c r="G10" s="102"/>
-      <c r="H10" s="98" t="s">
+      <c r="G10" s="131"/>
+      <c r="H10" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="98" t="s">
+      <c r="I10" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="97" t="s">
+    <row r="11" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="112" t="s">
+      <c r="B11" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="113" t="str">
+      <c r="C11" s="126" t="str">
         <f>Sheet1!F14</f>
         <v>Quyết toán kinh phí hoạt động đã tổ chức</v>
       </c>
-      <c r="D11" s="101"/>
-      <c r="E11" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F11" s="100">
+      <c r="D11" s="130"/>
+      <c r="E11" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F11" s="127">
         <f>Sheet1!I14</f>
         <v>46132</v>
       </c>
-      <c r="G11" s="102"/>
-      <c r="H11" s="98" t="s">
+      <c r="G11" s="131"/>
+      <c r="H11" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="I11" s="98" t="s">
+      <c r="I11" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="97" t="s">
+    <row r="12" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="112" t="s">
+      <c r="B12" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="113" t="str">
+      <c r="C12" s="126" t="str">
         <f>Sheet1!F15</f>
         <v>Phối hợp với văn phòng MTTQ bàn giao tài sản, nhà đất</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F12" s="100">
+      <c r="D12" s="130"/>
+      <c r="E12" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F12" s="127">
         <f>Sheet1!I15</f>
         <v>46132</v>
       </c>
-      <c r="G12" s="102"/>
-      <c r="H12" s="98" t="s">
+      <c r="G12" s="131"/>
+      <c r="H12" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="98" t="s">
+      <c r="I12" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="97" t="s">
+    <row r="13" spans="1:9" s="132" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A13" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="113" t="str">
+      <c r="C13" s="126" t="str">
         <f>Sheet1!F16</f>
         <v>Kê khai thông tin trên hệ thống Điều tra cơ sở hành chính, sự nghiệp của Bộ Nội vụ</v>
       </c>
-      <c r="D13" s="101"/>
-      <c r="E13" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F13" s="100">
+      <c r="D13" s="130"/>
+      <c r="E13" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F13" s="127">
         <v>46122</v>
       </c>
-      <c r="G13" s="102"/>
-      <c r="H13" s="98" t="s">
+      <c r="G13" s="131"/>
+      <c r="H13" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="98" t="s">
+      <c r="I13" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="97" t="s">
+    <row r="14" spans="1:9" s="132" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A14" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="113" t="str">
+      <c r="C14" s="126" t="str">
         <f>Sheet1!F17</f>
         <v>Tham mưu các nội dung bàn giao tài sản và trụ sở cơ quan cũ cho cấp có thẩm quyền</v>
       </c>
-      <c r="D14" s="101"/>
-      <c r="E14" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F14" s="100">
+      <c r="D14" s="130"/>
+      <c r="E14" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F14" s="127">
         <v>46122</v>
       </c>
-      <c r="G14" s="102"/>
-      <c r="H14" s="98" t="s">
+      <c r="G14" s="131"/>
+      <c r="H14" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I14" s="98" t="s">
+      <c r="I14" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="97" t="s">
+    <row r="15" spans="1:9" s="132" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A15" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="113" t="str">
+      <c r="C15" s="126" t="str">
         <f>Sheet1!F18</f>
         <v>Tiếp tục tham mưu giải quyết tồn động của các Tỉnh đoàn cũ (Dự án công viên Hoa Thanh niên; Sân bóng; Trung tâm SHDNTTN Bình Thuận</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F15" s="100">
+      <c r="D15" s="130"/>
+      <c r="E15" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F15" s="127">
         <v>46142</v>
       </c>
-      <c r="G15" s="102"/>
-      <c r="H15" s="98" t="s">
+      <c r="G15" s="131"/>
+      <c r="H15" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I15" s="98" t="s">
+      <c r="I15" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="97" t="s">
+    <row r="16" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="112" t="s">
+      <c r="B16" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="113" t="str">
+      <c r="C16" s="126" t="str">
         <f>Sheet1!F19</f>
         <v>Rà soát kết quả thực hiện BTC quý 1 triển khai nhiệm vụ quý 2</v>
       </c>
-      <c r="D16" s="101"/>
-      <c r="E16" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F16" s="100">
+      <c r="D16" s="130"/>
+      <c r="E16" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F16" s="127">
         <v>46142</v>
       </c>
-      <c r="G16" s="102"/>
-      <c r="H16" s="98" t="s">
+      <c r="G16" s="131"/>
+      <c r="H16" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="I16" s="98" t="s">
+      <c r="I16" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="97" t="s">
+    <row r="17" spans="1:9" s="132" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="112" t="s">
+      <c r="B17" s="76" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="113" t="str">
+      <c r="C17" s="126" t="str">
         <f>Sheet1!F20</f>
         <v>Lịch trực Ban nghĩ lễ Giỗ tổ Hùng Vương và 30/4</v>
       </c>
-      <c r="D17" s="101"/>
-      <c r="E17" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F17" s="100">
+      <c r="D17" s="130"/>
+      <c r="E17" s="127">
+        <v>46113</v>
+      </c>
+      <c r="F17" s="127">
         <v>46142</v>
       </c>
-      <c r="G17" s="102"/>
-      <c r="H17" s="98" t="s">
+      <c r="G17" s="131"/>
+      <c r="H17" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="98" t="s">
+      <c r="I17" s="76" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="97" t="s">
+    <row r="18" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="113" t="str">
+      <c r="C18" s="135" t="str">
         <f>Sheet1!F21</f>
         <v>Hướng dẫn tuyên truyền kỷ niệm 136 năm Ngày sinh Chỉ tịch Hồ Chí Minh</v>
       </c>
-      <c r="D18" s="101"/>
-      <c r="E18" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F18" s="100">
+      <c r="D18" s="136"/>
+      <c r="E18" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F18" s="137">
         <f>Sheet1!I21</f>
         <v>46132</v>
       </c>
-      <c r="G18" s="102"/>
-      <c r="H18" s="98" t="s">
+      <c r="G18" s="138"/>
+      <c r="H18" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I18" s="98" t="s">
+      <c r="I18" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="97" t="s">
+    <row r="19" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="114" t="s">
+      <c r="B19" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="113" t="str">
+      <c r="C19" s="135" t="str">
         <f>Sheet1!F22</f>
         <v>Báo cáo dư luận hàng tuần, tháng</v>
       </c>
-      <c r="D19" s="101"/>
-      <c r="E19" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F19" s="100">
+      <c r="D19" s="136"/>
+      <c r="E19" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F19" s="137">
         <v>46126</v>
       </c>
-      <c r="G19" s="102"/>
-      <c r="H19" s="98" t="s">
+      <c r="G19" s="138"/>
+      <c r="H19" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I19" s="98" t="s">
+      <c r="I19" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="97" t="s">
+    <row r="20" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="114" t="s">
+      <c r="B20" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="113" t="str">
+      <c r="C20" s="135" t="str">
         <f>Sheet1!F23</f>
         <v>KH, Thể lệ Cuộc thi trực tuyến tìm hiểu Nghị quyết Đại hội</v>
       </c>
-      <c r="D20" s="101"/>
-      <c r="E20" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F20" s="100">
+      <c r="D20" s="136"/>
+      <c r="E20" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F20" s="137">
         <v>46142</v>
       </c>
-      <c r="G20" s="102"/>
-      <c r="H20" s="98" t="s">
+      <c r="G20" s="138"/>
+      <c r="H20" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I20" s="98" t="s">
+      <c r="I20" s="134" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="97" t="s">
+    <row r="21" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="114" t="s">
+      <c r="B21" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="113" t="str">
+      <c r="C21" s="135" t="str">
         <f>Sheet1!F24</f>
         <v>QĐ trao giải Minigame tìm hiểu pháp luật về bầu cử</v>
       </c>
-      <c r="D21" s="101"/>
-      <c r="E21" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F21" s="100">
+      <c r="D21" s="136"/>
+      <c r="E21" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F21" s="137">
         <v>46142</v>
       </c>
-      <c r="G21" s="102"/>
-      <c r="H21" s="98" t="s">
+      <c r="G21" s="138"/>
+      <c r="H21" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I21" s="98" t="s">
+      <c r="I21" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="97" t="s">
+    <row r="22" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="114" t="s">
+      <c r="B22" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="113" t="str">
+      <c r="C22" s="135" t="str">
         <f>Sheet1!F25</f>
         <v>Các văn bản triển khai công tác 35 Tỉnh đoàn (văn bản mật, báo cáo định kỳ)</v>
       </c>
-      <c r="D22" s="101"/>
-      <c r="E22" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F22" s="100">
+      <c r="D22" s="136"/>
+      <c r="E22" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F22" s="137">
         <v>46142</v>
       </c>
-      <c r="G22" s="102"/>
-      <c r="H22" s="98" t="s">
+      <c r="G22" s="138"/>
+      <c r="H22" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I22" s="98" t="s">
+      <c r="I22" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="97" t="s">
+    <row r="23" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="114" t="s">
+      <c r="B23" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="113" t="str">
+      <c r="C23" s="135" t="str">
         <f>Sheet1!F26</f>
         <v>KH tổ chức Hành trình "Tuổi trẻ Lâm Đồng với biển đảo quê hương" năm 2026</v>
       </c>
-      <c r="D23" s="101"/>
-      <c r="E23" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F23" s="100">
+      <c r="D23" s="136"/>
+      <c r="E23" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F23" s="137">
         <f>Sheet1!I26</f>
         <v>46122</v>
       </c>
-      <c r="G23" s="102"/>
-      <c r="H23" s="98" t="s">
+      <c r="G23" s="138"/>
+      <c r="H23" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I23" s="98" t="s">
+      <c r="I23" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A24" s="97" t="s">
+    <row r="24" spans="1:9" s="139" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A24" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="114" t="s">
+      <c r="B24" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C24" s="113" t="str">
+      <c r="C24" s="135" t="str">
         <f>Sheet1!F27</f>
         <v xml:space="preserve"> KH tổ chức Liên hoan tuyên truyền ca khúc cách mạng tỉnh Lâm Đồng năm 2026</v>
       </c>
-      <c r="D24" s="101"/>
-      <c r="E24" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F24" s="100">
+      <c r="D24" s="136"/>
+      <c r="E24" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F24" s="137">
         <f>Sheet1!I27</f>
         <v>46122</v>
       </c>
-      <c r="G24" s="102"/>
-      <c r="H24" s="98" t="s">
+      <c r="G24" s="138"/>
+      <c r="H24" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I24" s="98" t="s">
+      <c r="I24" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="97" t="s">
+    <row r="25" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="113" t="str">
+      <c r="C25" s="135" t="str">
         <f>Sheet1!F28</f>
         <v>Báo cáo dư luận tháng 5</v>
       </c>
-      <c r="D25" s="101"/>
-      <c r="E25" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F25" s="100">
+      <c r="D25" s="136"/>
+      <c r="E25" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F25" s="137">
         <v>46132</v>
       </c>
-      <c r="G25" s="102"/>
-      <c r="H25" s="98" t="s">
+      <c r="G25" s="138"/>
+      <c r="H25" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I25" s="98" t="s">
+      <c r="I25" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="97" t="s">
+    <row r="26" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="114" t="s">
+      <c r="B26" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="113" t="str">
+      <c r="C26" s="135" t="str">
         <f>Sheet1!F29</f>
         <v>Hướng dẫn tuyên truyền tháng 5</v>
       </c>
-      <c r="D26" s="101"/>
-      <c r="E26" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F26" s="100">
+      <c r="D26" s="136"/>
+      <c r="E26" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F26" s="137">
         <v>46132</v>
       </c>
-      <c r="G26" s="102"/>
-      <c r="H26" s="98" t="s">
+      <c r="G26" s="138"/>
+      <c r="H26" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="98" t="s">
+      <c r="I26" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="97" t="s">
+    <row r="27" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="114" t="s">
+      <c r="B27" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="113" t="str">
+      <c r="C27" s="135" t="str">
         <f>Sheet1!F30</f>
         <v>CV giới thiệu nhân sự CTV Phòng chống tác hại của thuốc lá</v>
       </c>
-      <c r="D27" s="101"/>
-      <c r="E27" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F27" s="100">
+      <c r="D27" s="136"/>
+      <c r="E27" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F27" s="137">
         <v>46117</v>
       </c>
-      <c r="G27" s="102"/>
-      <c r="H27" s="98" t="s">
+      <c r="G27" s="138"/>
+      <c r="H27" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I27" s="98" t="s">
+      <c r="I27" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A28" s="97" t="s">
+    <row r="28" spans="1:9" s="139" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A28" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="114" t="s">
+      <c r="B28" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="113" t="str">
+      <c r="C28" s="135" t="str">
         <f>Sheet1!F31</f>
         <v xml:space="preserve"> KH tổ chức tuyên dương “Thanh niên tiên tiến làm theo lời Bác” nhân kỷ niệm 136 năm Ngày sinh Chủ tịch Hồ Chí Minh (19/5/1890 - 19/5/2026)</v>
       </c>
-      <c r="D28" s="101"/>
-      <c r="E28" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F28" s="100">
+      <c r="D28" s="136"/>
+      <c r="E28" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F28" s="137">
         <v>46127</v>
       </c>
-      <c r="G28" s="102"/>
-      <c r="H28" s="98" t="s">
+      <c r="G28" s="138"/>
+      <c r="H28" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="98" t="s">
+      <c r="I28" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="97" t="s">
+    <row r="29" spans="1:9" s="139" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A29" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="114" t="s">
+      <c r="B29" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="113" t="str">
+      <c r="C29" s="135" t="str">
         <f>Sheet1!F32</f>
         <v>Kế hoạch tuyên truyền, vận động đoàn viên thanh niên và nhân dân tham gia bảo hiểm y tế toàn dân năm 2026</v>
       </c>
-      <c r="D29" s="101"/>
-      <c r="E29" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F29" s="100">
+      <c r="D29" s="136"/>
+      <c r="E29" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F29" s="137">
         <v>46127</v>
       </c>
-      <c r="G29" s="102"/>
-      <c r="H29" s="98" t="s">
+      <c r="G29" s="138"/>
+      <c r="H29" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="I29" s="98" t="s">
+      <c r="I29" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="97" t="s">
+    <row r="30" spans="1:9" s="139" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A30" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="114" t="s">
+      <c r="B30" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="113" t="str">
+      <c r="C30" s="135" t="str">
         <f>Sheet1!F33</f>
         <v>Kế hoạch tuyên truyền phòng chống tác hại thuốc lá trong đoàn viên thanh niên năm 2026</v>
       </c>
-      <c r="D30" s="101"/>
-      <c r="E30" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F30" s="100" t="str">
+      <c r="D30" s="136"/>
+      <c r="E30" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F30" s="137" t="str">
         <f>Sheet1!I33</f>
         <v>15/4/2026</v>
       </c>
-      <c r="G30" s="102"/>
-      <c r="H30" s="98" t="s">
+      <c r="G30" s="138"/>
+      <c r="H30" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I30" s="98" t="s">
+      <c r="I30" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="97" t="s">
+    <row r="31" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="114" t="s">
+      <c r="B31" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C31" s="113" t="str">
+      <c r="C31" s="135" t="str">
         <f>Sheet1!F34</f>
         <v>Lễ Phát động Cuộc thi trực tuyến tìm hiểu Nghị quyết Đại hội</v>
       </c>
-      <c r="D31" s="101"/>
-      <c r="E31" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F31" s="100">
+      <c r="D31" s="136"/>
+      <c r="E31" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F31" s="137">
         <v>46118</v>
       </c>
-      <c r="G31" s="102"/>
-      <c r="H31" s="98" t="s">
+      <c r="G31" s="138"/>
+      <c r="H31" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I31" s="98" t="s">
+      <c r="I31" s="134" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="97" t="s">
+    <row r="32" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="114" t="s">
+      <c r="B32" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="113" t="str">
+      <c r="C32" s="135" t="str">
         <f>Sheet1!F35</f>
         <v>Trao giải Minigame tìm hiểu pháp luật về bầu cử</v>
       </c>
-      <c r="D32" s="101"/>
-      <c r="E32" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F32" s="100">
+      <c r="D32" s="136"/>
+      <c r="E32" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F32" s="137">
         <v>46129</v>
       </c>
-      <c r="G32" s="102"/>
-      <c r="H32" s="98" t="s">
+      <c r="G32" s="138"/>
+      <c r="H32" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I32" s="98" t="s">
+      <c r="I32" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="97" t="s">
+    <row r="33" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="114" t="s">
+      <c r="B33" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="113" t="str">
+      <c r="C33" s="135" t="str">
         <f>Sheet1!F36</f>
         <v>Tiếp tục ôn đốc đăng tải triển khai Đề án Những câu chuyện thời hoa lửa</v>
       </c>
-      <c r="D33" s="101"/>
-      <c r="E33" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F33" s="100">
+      <c r="D33" s="136"/>
+      <c r="E33" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F33" s="137">
         <v>46142</v>
       </c>
-      <c r="G33" s="102"/>
-      <c r="H33" s="98" t="s">
+      <c r="G33" s="138"/>
+      <c r="H33" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I33" s="98" t="s">
+      <c r="I33" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="97" t="s">
+    <row r="34" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="114" t="s">
+      <c r="B34" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="113" t="str">
+      <c r="C34" s="135" t="str">
         <f>Sheet1!F37</f>
         <v>Tham mưu các nội dung liên quan đến Lễ hội Giỗ tổ Hùng Vương</v>
       </c>
-      <c r="D34" s="101"/>
-      <c r="E34" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F34" s="100">
+      <c r="D34" s="136"/>
+      <c r="E34" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F34" s="137">
         <v>46138</v>
       </c>
-      <c r="G34" s="102"/>
-      <c r="H34" s="98" t="s">
+      <c r="G34" s="138"/>
+      <c r="H34" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I34" s="98" t="s">
+      <c r="I34" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A35" s="97" t="s">
+    <row r="35" spans="1:9" s="139" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A35" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="114" t="s">
+      <c r="B35" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="113" t="str">
+      <c r="C35" s="135" t="str">
         <f>Sheet1!F38</f>
         <v>Tổ chức Chương trình sinh hoạt chính trị  nhân kỷ niệm 51 năm Giải phóng miền Nam, thống nhất đất nước ngày (30/4/1975 - 30/4/2026)</v>
       </c>
-      <c r="D35" s="101"/>
-      <c r="E35" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F35" s="100">
+      <c r="D35" s="136"/>
+      <c r="E35" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F35" s="137">
         <v>46122</v>
       </c>
-      <c r="G35" s="102"/>
-      <c r="H35" s="98" t="s">
+      <c r="G35" s="138"/>
+      <c r="H35" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="I35" s="98" t="s">
+      <c r="I35" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A36" s="97" t="s">
+    <row r="36" spans="1:9" s="139" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A36" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C36" s="113" t="str">
+      <c r="C36" s="135" t="str">
         <f>Sheet1!F39</f>
         <v>Tham mưu gửi ấn phẩm phục vụ biên soạn các ấn phẩm chào mừng Đại hội Đoàn toàn quốc lần thứ XII</v>
       </c>
-      <c r="D36" s="101"/>
-      <c r="E36" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F36" s="100">
+      <c r="D36" s="136"/>
+      <c r="E36" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F36" s="137">
         <v>46129</v>
       </c>
-      <c r="G36" s="102"/>
-      <c r="H36" s="98" t="s">
+      <c r="G36" s="138"/>
+      <c r="H36" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I36" s="98" t="s">
+      <c r="I36" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="97" t="s">
+    <row r="37" spans="1:9" s="139" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="114" t="s">
+      <c r="B37" s="134" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="113" t="str">
+      <c r="C37" s="135" t="str">
         <f>Sheet1!F40</f>
         <v>Tuyên truyền kịp thời các hoạt động tập trung cấp tỉnh trong tháng</v>
       </c>
-      <c r="D37" s="101"/>
-      <c r="E37" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F37" s="100">
+      <c r="D37" s="136"/>
+      <c r="E37" s="137">
+        <v>46113</v>
+      </c>
+      <c r="F37" s="137">
         <v>46142</v>
       </c>
-      <c r="G37" s="102"/>
-      <c r="H37" s="98" t="s">
+      <c r="G37" s="138"/>
+      <c r="H37" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="I37" s="98" t="s">
+      <c r="I37" s="134" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="97" t="s">
+    <row r="38" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="115" t="s">
+      <c r="B38" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C38" s="113" t="str">
+      <c r="C38" s="142" t="str">
         <f>Sheet1!F41</f>
         <v>Kế hoạch rà soát quy hoạch các chức danh chủ chốt của Đoàn năm 2026</v>
       </c>
-      <c r="D38" s="101"/>
-      <c r="E38" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F38" s="100">
+      <c r="D38" s="143"/>
+      <c r="E38" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F38" s="144">
         <v>46122</v>
       </c>
-      <c r="G38" s="102"/>
-      <c r="H38" s="98" t="s">
+      <c r="G38" s="145"/>
+      <c r="H38" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="98" t="s">
+      <c r="I38" s="141" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A39" s="97" t="s">
+    <row r="39" spans="1:9" s="146" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A39" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="115" t="s">
+      <c r="B39" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="113" t="str">
+      <c r="C39" s="142" t="str">
         <f>Sheet1!F42</f>
         <v>CV góp ý dự thảo hướng dẫn quy trình thủ tục kiện toàn bổ sung nhân sự cấp tỉnh</v>
       </c>
-      <c r="D39" s="101"/>
-      <c r="E39" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F39" s="100">
+      <c r="D39" s="143"/>
+      <c r="E39" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F39" s="144">
         <v>46114</v>
       </c>
-      <c r="G39" s="102"/>
-      <c r="H39" s="98" t="s">
+      <c r="G39" s="145"/>
+      <c r="H39" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I39" s="98" t="s">
+      <c r="I39" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A40" s="97" t="s">
+    <row r="40" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="115" t="s">
+      <c r="B40" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="113" t="str">
+      <c r="C40" s="142" t="str">
         <f>Sheet1!F43</f>
         <v>CV góp ý dự thảo Hướng dẫn một số vấn đề cụ thể thi hành Điều lệ Đảng</v>
       </c>
-      <c r="D40" s="101"/>
-      <c r="E40" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F40" s="100">
+      <c r="D40" s="143"/>
+      <c r="E40" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F40" s="144">
         <v>46116</v>
       </c>
-      <c r="G40" s="102"/>
-      <c r="H40" s="98" t="s">
+      <c r="G40" s="145"/>
+      <c r="H40" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="I40" s="98" t="s">
+      <c r="I40" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A41" s="97" t="s">
+    <row r="41" spans="1:9" s="146" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A41" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="115" t="s">
+      <c r="B41" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="113" t="str">
+      <c r="C41" s="142" t="str">
         <f>Sheet1!F45</f>
         <v>Văn bản triển khai thực hiện các nội dung liên quan phần mềm Quản lý đoàn viên</v>
       </c>
-      <c r="D41" s="101"/>
-      <c r="E41" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F41" s="100">
+      <c r="D41" s="143"/>
+      <c r="E41" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F41" s="144">
         <v>46132</v>
       </c>
-      <c r="G41" s="102"/>
-      <c r="H41" s="98" t="s">
+      <c r="G41" s="145"/>
+      <c r="H41" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="I41" s="98" t="s">
+      <c r="I41" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A42" s="97" t="s">
+    <row r="42" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="115" t="s">
+      <c r="B42" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="113" t="str">
+      <c r="C42" s="142" t="str">
         <f>Sheet1!F46</f>
         <v>Văn bản triển khai thực hiện kiểm tra, giám sát</v>
       </c>
-      <c r="D42" s="101"/>
-      <c r="E42" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F42" s="100">
+      <c r="D42" s="143"/>
+      <c r="E42" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F42" s="144">
         <v>46132</v>
       </c>
-      <c r="G42" s="102"/>
-      <c r="H42" s="98" t="s">
+      <c r="G42" s="145"/>
+      <c r="H42" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="98" t="s">
+      <c r="I42" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A43" s="97" t="s">
+    <row r="43" spans="1:9" s="146" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A43" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="115" t="s">
+      <c r="B43" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="113" t="str">
+      <c r="C43" s="142" t="str">
         <f>Sheet1!F47</f>
         <v>Kế hoạch giao chỉ tiêu phát triển đoàn viên; giới thiệu đoàn viên ưu tú cho Đảng và phát triển đảng viên trong ĐVTN năm 2026</v>
       </c>
-      <c r="D43" s="101"/>
-      <c r="E43" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F43" s="100">
+      <c r="D43" s="143"/>
+      <c r="E43" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F43" s="144">
         <v>46132</v>
       </c>
-      <c r="G43" s="102"/>
-      <c r="H43" s="98" t="s">
+      <c r="G43" s="145"/>
+      <c r="H43" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I43" s="98" t="s">
+      <c r="I43" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A44" s="97" t="s">
+    <row r="44" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="115" t="s">
+      <c r="B44" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="113" t="str">
+      <c r="C44" s="142" t="str">
         <f>Sheet1!F48</f>
         <v>Báo cáo công tác phòng, chống tham nhũng, lãng phí tiêu cực tháng 4/2026</v>
       </c>
-      <c r="D44" s="101"/>
-      <c r="E44" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F44" s="100">
+      <c r="D44" s="143"/>
+      <c r="E44" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F44" s="144">
         <v>46132</v>
       </c>
-      <c r="G44" s="102"/>
-      <c r="H44" s="98" t="s">
+      <c r="G44" s="145"/>
+      <c r="H44" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I44" s="98" t="s">
+      <c r="I44" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A45" s="97" t="s">
+    <row r="45" spans="1:9" s="146" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A45" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="115" t="s">
+      <c r="B45" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C45" s="113" t="str">
+      <c r="C45" s="142" t="str">
         <f>Sheet1!F49</f>
         <v>Đôn đốc triển khai thực hiện các nội dung liên quan phần mềm Quản lý đoàn viên</v>
       </c>
-      <c r="D45" s="101"/>
-      <c r="E45" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F45" s="100">
+      <c r="D45" s="143"/>
+      <c r="E45" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F45" s="144">
         <v>46142</v>
       </c>
-      <c r="G45" s="102"/>
-      <c r="H45" s="98" t="s">
+      <c r="G45" s="145"/>
+      <c r="H45" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I45" s="98" t="s">
+      <c r="I45" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A46" s="97" t="s">
+    <row r="46" spans="1:9" s="146" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A46" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B46" s="115" t="s">
+      <c r="B46" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="113" t="str">
+      <c r="C46" s="142" t="str">
         <f>Sheet1!F50</f>
         <v>Triển khai các nội dung liên quan đến việc thành lập tổ chức Đoàn trong doanh nghiệp ngoài Nhà nước</v>
       </c>
-      <c r="D46" s="101"/>
-      <c r="E46" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F46" s="100">
+      <c r="D46" s="143"/>
+      <c r="E46" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F46" s="144">
         <v>46127</v>
       </c>
-      <c r="G46" s="102"/>
-      <c r="H46" s="98" t="s">
+      <c r="G46" s="145"/>
+      <c r="H46" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I46" s="98" t="s">
+      <c r="I46" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="97" t="s">
+    <row r="47" spans="1:9" s="146" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="115" t="s">
+      <c r="B47" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C47" s="113" t="s">
+      <c r="C47" s="142" t="s">
         <v>183</v>
       </c>
-      <c r="D47" s="101"/>
-      <c r="E47" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F47" s="100">
+      <c r="D47" s="143"/>
+      <c r="E47" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F47" s="144">
         <v>46132</v>
       </c>
-      <c r="G47" s="102"/>
-      <c r="H47" s="98" t="s">
+      <c r="G47" s="145"/>
+      <c r="H47" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="I47" s="98" t="s">
+      <c r="I47" s="141" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A48" s="97" t="s">
+    <row r="48" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="115" t="s">
+      <c r="B48" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="113" t="str">
+      <c r="C48" s="142" t="str">
         <f>Sheet1!F53</f>
         <v>Tham mưu các nội dung liên quan đến các hợp đồng lao động ngoài biên chế</v>
       </c>
-      <c r="D48" s="101"/>
-      <c r="E48" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F48" s="100">
+      <c r="D48" s="143"/>
+      <c r="E48" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F48" s="144">
         <v>46127</v>
       </c>
-      <c r="G48" s="102"/>
-      <c r="H48" s="98" t="s">
+      <c r="G48" s="145"/>
+      <c r="H48" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I48" s="98" t="s">
+      <c r="I48" s="141" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A49" s="97" t="s">
+    <row r="49" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="115" t="s">
+      <c r="B49" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C49" s="113" t="str">
+      <c r="C49" s="142" t="str">
         <f>Sheet1!F54</f>
         <v>Kiểm tra, giám sát cơ sở</v>
       </c>
-      <c r="D49" s="101"/>
-      <c r="E49" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F49" s="100">
+      <c r="D49" s="143"/>
+      <c r="E49" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F49" s="144">
         <v>46142</v>
       </c>
-      <c r="G49" s="102"/>
-      <c r="H49" s="98" t="s">
+      <c r="G49" s="145"/>
+      <c r="H49" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I49" s="98" t="s">
+      <c r="I49" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A50" s="97" t="s">
+    <row r="50" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B50" s="115" t="s">
+      <c r="B50" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="113" t="str">
+      <c r="C50" s="142" t="str">
         <f>Sheet1!F56</f>
         <v>Triển khai đăng tải tài liệu sinh hoạt chi đoàn tháng 4/2026</v>
       </c>
-      <c r="D50" s="101"/>
-      <c r="E50" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F50" s="100">
+      <c r="D50" s="143"/>
+      <c r="E50" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F50" s="144">
         <v>46121</v>
       </c>
-      <c r="G50" s="102"/>
-      <c r="H50" s="98" t="s">
+      <c r="G50" s="145"/>
+      <c r="H50" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I50" s="98" t="s">
+      <c r="I50" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A51" s="97" t="s">
+    <row r="51" spans="1:9" s="146" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="115" t="s">
+      <c r="B51" s="141" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="113" t="str">
+      <c r="C51" s="142" t="str">
         <f>Sheet1!F57</f>
         <v>Phối hợp tham mưu công tác nhân sự của Hội LHTN Việt Nam tỉnh</v>
       </c>
-      <c r="D51" s="101"/>
-      <c r="E51" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F51" s="100">
+      <c r="D51" s="143"/>
+      <c r="E51" s="144">
+        <v>46113</v>
+      </c>
+      <c r="F51" s="144">
         <v>46137</v>
       </c>
-      <c r="G51" s="102"/>
-      <c r="H51" s="98" t="s">
+      <c r="G51" s="145"/>
+      <c r="H51" s="141" t="s">
         <v>174</v>
       </c>
-      <c r="I51" s="98" t="s">
+      <c r="I51" s="141" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A52" s="117" t="s">
+    <row r="52" spans="1:9" s="152" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A52" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B52" s="116" t="s">
+      <c r="B52" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="113" t="str">
+      <c r="C52" s="148" t="str">
         <f>Sheet1!F60</f>
         <v>KH triển khai Đề án "Thanh niên tham gia bảo tồn, phát huy bản sắc văn hóa dân tộc Việt Nam"</v>
       </c>
-      <c r="D52" s="101"/>
-      <c r="E52" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F52" s="100">
+      <c r="D52" s="149"/>
+      <c r="E52" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F52" s="150">
         <v>46127</v>
       </c>
-      <c r="G52" s="102"/>
-      <c r="H52" s="98" t="s">
+      <c r="G52" s="151"/>
+      <c r="H52" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="I52" s="98" t="s">
+      <c r="I52" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="117" t="s">
+    <row r="53" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B53" s="116" t="s">
+      <c r="B53" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C53" s="113" t="str">
+      <c r="C53" s="148" t="str">
         <f>Sheet1!F61</f>
         <v>KH Thắp sáng ước mơ hoàn lương</v>
       </c>
-      <c r="D53" s="101"/>
-      <c r="E53" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F53" s="100">
+      <c r="D53" s="149"/>
+      <c r="E53" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F53" s="150">
         <v>46122</v>
       </c>
-      <c r="G53" s="102"/>
-      <c r="H53" s="98" t="s">
+      <c r="G53" s="151"/>
+      <c r="H53" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="I53" s="98" t="s">
+      <c r="I53" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="117" t="s">
+    <row r="54" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B54" s="116" t="s">
+      <c r="B54" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C54" s="113" t="str">
+      <c r="C54" s="148" t="str">
         <f>Sheet1!F62</f>
         <v>Báo cáo tổng kết Tháng Thanh niên năm 2026</v>
       </c>
-      <c r="D54" s="101"/>
-      <c r="E54" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F54" s="100">
+      <c r="D54" s="149"/>
+      <c r="E54" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F54" s="150">
         <v>46118</v>
       </c>
-      <c r="G54" s="102"/>
-      <c r="H54" s="98" t="s">
+      <c r="G54" s="151"/>
+      <c r="H54" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="I54" s="98" t="s">
+      <c r="I54" s="79" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="117" t="s">
+    <row r="55" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B55" s="116" t="s">
+      <c r="B55" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C55" s="113" t="str">
+      <c r="C55" s="148" t="str">
         <f>Sheet1!F63</f>
         <v>Dự thảo Đề án hỗ trợ thanh niên khởi nghiệp</v>
       </c>
-      <c r="D55" s="101"/>
-      <c r="E55" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F55" s="100">
+      <c r="D55" s="149"/>
+      <c r="E55" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F55" s="150">
         <v>46140</v>
       </c>
-      <c r="G55" s="102"/>
-      <c r="H55" s="98" t="s">
+      <c r="G55" s="151"/>
+      <c r="H55" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I55" s="98" t="s">
+      <c r="I55" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="117" t="s">
+    <row r="56" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="116" t="s">
+      <c r="B56" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C56" s="113" t="str">
+      <c r="C56" s="148" t="str">
         <f>Sheet1!F64</f>
         <v>Kế hoạch hỗ trợ thanh niên khởi nghiệp tỉnh Lâm Đồng năm 2026</v>
       </c>
-      <c r="D56" s="101"/>
-      <c r="E56" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F56" s="100">
+      <c r="D56" s="149"/>
+      <c r="E56" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F56" s="150">
         <v>46141</v>
       </c>
-      <c r="G56" s="102"/>
-      <c r="H56" s="98" t="s">
+      <c r="G56" s="151"/>
+      <c r="H56" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="I56" s="98" t="s">
+      <c r="I56" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A57" s="117" t="s">
+    <row r="57" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B57" s="116" t="s">
+      <c r="B57" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C57" s="113" t="str">
+      <c r="C57" s="148" t="str">
         <f>Sheet1!F65</f>
         <v>Dự thảo Kế hoạch tổ chức Hội trại tập huấn kỹ năng cán bộ Đoàn - Hội</v>
       </c>
-      <c r="D57" s="101"/>
-      <c r="E57" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F57" s="100">
+      <c r="D57" s="149"/>
+      <c r="E57" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F57" s="150">
         <v>46141</v>
       </c>
-      <c r="G57" s="102"/>
-      <c r="H57" s="98" t="s">
+      <c r="G57" s="151"/>
+      <c r="H57" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="I57" s="98" t="s">
+      <c r="I57" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A58" s="117" t="s">
+    <row r="58" spans="1:9" s="152" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+      <c r="A58" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B58" s="116" t="s">
+      <c r="B58" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C58" s="113" t="str">
+      <c r="C58" s="148" t="str">
         <f>Sheet1!F66</f>
         <v>Hướng dẫn triển khai một số nội dung trọng tâm phong trào "Tuổi trẻ chung tay xây dựng nông thôn mới và chương trình bảo vệ môi trường ứng phó với biến đổi khi hậu</v>
       </c>
-      <c r="D58" s="101"/>
-      <c r="E58" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F58" s="100">
+      <c r="D58" s="149"/>
+      <c r="E58" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F58" s="150">
         <v>46140</v>
       </c>
-      <c r="G58" s="102"/>
-      <c r="H58" s="98" t="s">
+      <c r="G58" s="151"/>
+      <c r="H58" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I58" s="98" t="s">
+      <c r="I58" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A59" s="117" t="s">
+    <row r="59" spans="1:9" s="152" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A59" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="116" t="s">
+      <c r="B59" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C59" s="113" t="str">
+      <c r="C59" s="148" t="str">
         <f>Sheet1!F67</f>
         <v>Kế hoạch tổ chức ngày hội Thanh niên công nhân và tuyên dương Thanh niên công nhân tiêu biểu năm 2026</v>
       </c>
-      <c r="D59" s="101"/>
-      <c r="E59" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F59" s="100">
+      <c r="D59" s="149"/>
+      <c r="E59" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F59" s="150">
         <v>46127</v>
       </c>
-      <c r="G59" s="102"/>
-      <c r="H59" s="98" t="s">
+      <c r="G59" s="151"/>
+      <c r="H59" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="I59" s="98" t="s">
+      <c r="I59" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="117" t="s">
+    <row r="60" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B60" s="116" t="s">
+      <c r="B60" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C60" s="113" t="str">
+      <c r="C60" s="148" t="str">
         <f>Sheet1!F68</f>
         <v>Kế hoạch tổ chức ngày Thầy thuốc trẻ làm theo lời Bác</v>
       </c>
-      <c r="D60" s="101"/>
-      <c r="E60" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F60" s="100">
+      <c r="D60" s="149"/>
+      <c r="E60" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F60" s="150">
         <v>46136</v>
       </c>
-      <c r="G60" s="102"/>
-      <c r="H60" s="98" t="s">
+      <c r="G60" s="151"/>
+      <c r="H60" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="I60" s="98" t="s">
+      <c r="I60" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A61" s="117" t="s">
+    <row r="61" spans="1:9" s="152" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A61" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B61" s="116" t="s">
+      <c r="B61" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="113" t="str">
+      <c r="C61" s="148" t="str">
         <f>Sheet1!F69</f>
         <v>Công văn chủ động, đẩy mạnh triển khai phong trào thi đua Bình dân học vụ số trong đoàn viên thanh niên năm 2026</v>
       </c>
-      <c r="D61" s="101"/>
-      <c r="E61" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F61" s="100">
+      <c r="D61" s="149"/>
+      <c r="E61" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F61" s="150">
         <v>46115</v>
       </c>
-      <c r="G61" s="102"/>
-      <c r="H61" s="98" t="s">
+      <c r="G61" s="151"/>
+      <c r="H61" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I61" s="98" t="s">
+      <c r="I61" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A62" s="117" t="s">
+    <row r="62" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B62" s="116" t="s">
+      <c r="B62" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="113" t="str">
+      <c r="C62" s="148" t="str">
         <f>Sheet1!F70</f>
         <v>Công văn triển khai cuộc thi khởi nghiệp thanh niên nông thôn của TWĐ</v>
       </c>
-      <c r="D62" s="101"/>
-      <c r="E62" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F62" s="100">
+      <c r="D62" s="149"/>
+      <c r="E62" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F62" s="150">
         <v>46119</v>
       </c>
-      <c r="G62" s="102"/>
-      <c r="H62" s="98" t="s">
+      <c r="G62" s="151"/>
+      <c r="H62" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I62" s="98" t="s">
+      <c r="I62" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="117" t="s">
+    <row r="63" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B63" s="116" t="s">
+      <c r="B63" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C63" s="113" t="str">
+      <c r="C63" s="148" t="str">
         <f>Sheet1!F71</f>
         <v>KH Tham mưu xóa 01 điểm đen ô nhiễm</v>
       </c>
-      <c r="D63" s="101"/>
-      <c r="E63" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F63" s="100">
+      <c r="D63" s="149"/>
+      <c r="E63" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F63" s="150">
         <v>46136</v>
       </c>
-      <c r="G63" s="102"/>
-      <c r="H63" s="98" t="s">
+      <c r="G63" s="151"/>
+      <c r="H63" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="I63" s="98" t="s">
+      <c r="I63" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="117" t="s">
+    <row r="64" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B64" s="116" t="s">
+      <c r="B64" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C64" s="113" t="str">
+      <c r="C64" s="148" t="str">
         <f>Sheet1!F73</f>
         <v>Kiện toàn các nguồn quỹ của Đoàn</v>
       </c>
-      <c r="D64" s="101"/>
-      <c r="E64" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F64" s="100">
+      <c r="D64" s="149"/>
+      <c r="E64" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F64" s="150">
         <v>46142</v>
       </c>
-      <c r="G64" s="102"/>
-      <c r="H64" s="98" t="s">
+      <c r="G64" s="151"/>
+      <c r="H64" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="I64" s="98" t="s">
+      <c r="I64" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="117" t="s">
+    <row r="65" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B65" s="116" t="s">
+      <c r="B65" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C65" s="113" t="str">
+      <c r="C65" s="148" t="str">
         <f>Sheet1!F74</f>
         <v>Hồ sơ khen thưởng Tháng thanh niên</v>
       </c>
-      <c r="D65" s="101"/>
-      <c r="E65" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F65" s="100">
+      <c r="D65" s="149"/>
+      <c r="E65" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F65" s="150">
         <v>46122</v>
       </c>
-      <c r="G65" s="102"/>
-      <c r="H65" s="98" t="s">
+      <c r="G65" s="151"/>
+      <c r="H65" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I65" s="98" t="s">
+      <c r="I65" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A66" s="117" t="s">
+    <row r="66" spans="1:9" s="152" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A66" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B66" s="116" t="s">
+      <c r="B66" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C66" s="113" t="str">
+      <c r="C66" s="148" t="str">
         <f>Sheet1!F75</f>
         <v>Phối hợp tổ chức chương trình “Gửi tiết kiệm chung tay vì người nghèo” năm 2026</v>
       </c>
-      <c r="D66" s="101"/>
-      <c r="E66" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F66" s="100">
+      <c r="D66" s="149"/>
+      <c r="E66" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F66" s="150">
         <v>46114</v>
       </c>
-      <c r="G66" s="102"/>
-      <c r="H66" s="98" t="s">
+      <c r="G66" s="151"/>
+      <c r="H66" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="I66" s="98" t="s">
+      <c r="I66" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="117" t="s">
+    <row r="67" spans="1:9" s="152" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B67" s="116" t="s">
+      <c r="B67" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C67" s="113" t="str">
+      <c r="C67" s="148" t="str">
         <f>Sheet1!F76</f>
         <v>Tổ chức tổng kết tháng thanh niên 2026</v>
       </c>
-      <c r="D67" s="101"/>
-      <c r="E67" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F67" s="100">
+      <c r="D67" s="149"/>
+      <c r="E67" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F67" s="150">
         <v>46129</v>
       </c>
-      <c r="G67" s="102"/>
-      <c r="H67" s="98" t="s">
+      <c r="G67" s="151"/>
+      <c r="H67" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I67" s="98" t="s">
+      <c r="I67" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A68" s="117" t="s">
+    <row r="68" spans="1:9" s="152" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+      <c r="A68" s="147" t="s">
         <v>7</v>
       </c>
-      <c r="B68" s="116" t="s">
+      <c r="B68" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="113" t="str">
+      <c r="C68" s="148" t="str">
         <f>Sheet1!F77</f>
         <v>Tham mưu các điều kiện hưởng phát động“Tết trồng cây đời đời nhớ ơn Bác Hồ” và trồng rừng tập trung, trồng cây phân tán năm 2026 do UBND tỉnh tổ chức</v>
       </c>
-      <c r="D68" s="101"/>
-      <c r="E68" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F68" s="100">
+      <c r="D68" s="149"/>
+      <c r="E68" s="150">
+        <v>46113</v>
+      </c>
+      <c r="F68" s="150">
         <v>46141</v>
       </c>
-      <c r="G68" s="102"/>
-      <c r="H68" s="98" t="s">
+      <c r="G68" s="151"/>
+      <c r="H68" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="I68" s="98" t="s">
+      <c r="I68" s="79" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A69" s="117" t="s">
+    <row r="69" spans="1:9" s="159" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A69" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="B69" s="119" t="s">
+      <c r="B69" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="113" t="str">
+      <c r="C69" s="155" t="str">
         <f>Sheet1!F78</f>
         <v>Văn bản phối hợp với Hội Doanh nhân trẻ tỉnh về việc phối hợp hỗ trợ tổ chức Diễn đàn Kinh tế tư nhân Việt Nam (VPSF) 2026</v>
       </c>
-      <c r="D69" s="101"/>
-      <c r="E69" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F69" s="100">
+      <c r="D69" s="156"/>
+      <c r="E69" s="157">
+        <v>46113</v>
+      </c>
+      <c r="F69" s="157">
         <v>46132</v>
       </c>
-      <c r="G69" s="102"/>
-      <c r="H69" s="98" t="s">
+      <c r="G69" s="158"/>
+      <c r="H69" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="I69" s="98" t="s">
+      <c r="I69" s="154" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A70" s="117" t="s">
+    <row r="70" spans="1:9" s="159" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+      <c r="A70" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="B70" s="119" t="s">
+      <c r="B70" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="113" t="str">
+      <c r="C70" s="155" t="str">
         <f>Sheet1!F79</f>
         <v>Các văn bản chuẩn bị Đại hội Hội LHTN VN tỉnh: Quyết định thành lập các tiểu Ban phục vụ Đại hội; các Đề án Đại hội; Chương trình, Kịch bản ĐH; Báo cáo chính trị Đại hội; Nghị quyết ĐH,...</v>
       </c>
-      <c r="D70" s="101"/>
-      <c r="E70" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F70" s="100">
+      <c r="D70" s="156"/>
+      <c r="E70" s="157">
+        <v>46113</v>
+      </c>
+      <c r="F70" s="157">
         <v>46141</v>
       </c>
-      <c r="G70" s="102"/>
-      <c r="H70" s="98" t="s">
+      <c r="G70" s="158"/>
+      <c r="H70" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="I70" s="98" t="s">
+      <c r="I70" s="154" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A71" s="117" t="s">
+    <row r="71" spans="1:9" s="159" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A71" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="B71" s="119" t="s">
+      <c r="B71" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="113" t="str">
+      <c r="C71" s="155" t="str">
         <f>Sheet1!F80</f>
         <v>Rà soát đôn đốc hoàn thành việc thành lập Hội LHTN Việt Nam các xã phường đặc khu</v>
       </c>
-      <c r="D71" s="101"/>
-      <c r="E71" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F71" s="100">
+      <c r="D71" s="156"/>
+      <c r="E71" s="157">
+        <v>46113</v>
+      </c>
+      <c r="F71" s="157">
         <v>46142</v>
       </c>
-      <c r="G71" s="102"/>
-      <c r="H71" s="98" t="s">
+      <c r="G71" s="158"/>
+      <c r="H71" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="I71" s="98" t="s">
+      <c r="I71" s="154" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="117" t="s">
+    <row r="72" spans="1:9" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="B72" s="119" t="s">
+      <c r="B72" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="C72" s="113" t="str">
+      <c r="C72" s="155" t="str">
         <f>Sheet1!F81</f>
         <v>Tham mưu các điều kiện chuẩn bị tổ chức ĐH Hội lần I</v>
       </c>
-      <c r="D72" s="101"/>
-      <c r="E72" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F72" s="100">
+      <c r="D72" s="156"/>
+      <c r="E72" s="157">
+        <v>46113</v>
+      </c>
+      <c r="F72" s="157">
         <v>46142</v>
       </c>
-      <c r="G72" s="102"/>
-      <c r="H72" s="98" t="s">
+      <c r="G72" s="158"/>
+      <c r="H72" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="I72" s="98" t="s">
+      <c r="I72" s="154" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="117" t="s">
+    <row r="73" spans="1:9" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="B73" s="119" t="s">
+      <c r="B73" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="113" t="str">
+      <c r="C73" s="155" t="str">
         <f>Sheet1!F82</f>
         <v>Tham mưu phân công dự chỉ đạo Đại hội Hội LHTN Việt Nam cơ sở</v>
       </c>
-      <c r="D73" s="101"/>
-      <c r="E73" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F73" s="100">
+      <c r="D73" s="156"/>
+      <c r="E73" s="157">
+        <v>46113</v>
+      </c>
+      <c r="F73" s="157">
         <v>46122</v>
       </c>
-      <c r="G73" s="102"/>
-      <c r="H73" s="98" t="s">
+      <c r="G73" s="158"/>
+      <c r="H73" s="154" t="s">
         <v>180</v>
       </c>
-      <c r="I73" s="98" t="s">
+      <c r="I73" s="154" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="117" t="s">
+    <row r="74" spans="1:9" s="159" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="153" t="s">
         <v>7</v>
       </c>
-      <c r="B74" s="119" t="s">
+      <c r="B74" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="C74" s="113" t="str">
+      <c r="C74" s="155" t="str">
         <f>Sheet1!F83</f>
         <v>Phối hợp rà soát thành lập Hội doanh nhân trẻ tỉnh Lâm Đồng</v>
       </c>
-      <c r="D74" s="101"/>
-      <c r="E74" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F74" s="100">
+      <c r="D74" s="156"/>
+      <c r="E74" s="157">
+        <v>46113</v>
+      </c>
+      <c r="F74" s="157">
         <v>46142</v>
       </c>
-      <c r="G74" s="102"/>
-      <c r="H74" s="98" t="s">
+      <c r="G74" s="158"/>
+      <c r="H74" s="154" t="s">
         <v>20</v>
       </c>
-      <c r="I74" s="98" t="s">
+      <c r="I74" s="154" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="118" t="s">
+    <row r="75" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B75" s="120" t="s">
+      <c r="B75" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C75" s="113" t="str">
+      <c r="C75" s="161" t="str">
         <f>Sheet1!F85</f>
         <v>Đề cương tuyên truyền 85 năm thành lập Đội</v>
       </c>
-      <c r="D75" s="101"/>
-      <c r="E75" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F75" s="100">
+      <c r="D75" s="162"/>
+      <c r="E75" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F75" s="163">
         <v>46122</v>
       </c>
-      <c r="G75" s="102"/>
-      <c r="H75" s="98" t="s">
+      <c r="G75" s="164"/>
+      <c r="H75" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="I75" s="98" t="s">
+      <c r="I75" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="118" t="s">
+    <row r="76" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B76" s="120" t="s">
+      <c r="B76" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C76" s="113" t="str">
+      <c r="C76" s="161" t="str">
         <f>Sheet1!F86</f>
         <v>Tờ tình TW về đề xuất xét trao tặng Cánh én hồng</v>
       </c>
-      <c r="D76" s="101"/>
-      <c r="E76" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F76" s="100">
+      <c r="D76" s="162"/>
+      <c r="E76" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F76" s="163">
         <v>46122</v>
       </c>
-      <c r="G76" s="102"/>
-      <c r="H76" s="98" t="s">
+      <c r="G76" s="164"/>
+      <c r="H76" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="I76" s="98" t="s">
+      <c r="I76" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A77" s="118" t="s">
+    <row r="77" spans="1:9" s="165" customFormat="1" ht="42" x14ac:dyDescent="0.2">
+      <c r="A77" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B77" s="120" t="s">
+      <c r="B77" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C77" s="113" t="str">
+      <c r="C77" s="161" t="str">
         <f>Sheet1!F87</f>
         <v>Ban hành KH tổ chức tập huấn cho cán bộ Hội đồng Đội về công tác bảo vệ, chăm sóc, giá dục thiếu niên nhi đồng sau khi thực hiện chính quyền địa phương 2 cấp</v>
       </c>
-      <c r="D77" s="101"/>
-      <c r="E77" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F77" s="100">
+      <c r="D77" s="162"/>
+      <c r="E77" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F77" s="163">
         <v>46142</v>
       </c>
-      <c r="G77" s="102"/>
-      <c r="H77" s="98" t="s">
+      <c r="G77" s="164"/>
+      <c r="H77" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="I77" s="98" t="s">
+      <c r="I77" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A78" s="118" t="s">
+    <row r="78" spans="1:9" s="165" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A78" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B78" s="120" t="s">
+      <c r="B78" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C78" s="113" t="str">
+      <c r="C78" s="161" t="str">
         <f>Sheet1!F88</f>
         <v>Tham mưu các vb triển khai đăng cai  Festival Thiếu nhi toàn quốc lần thứ nhất - năm 2026</v>
       </c>
-      <c r="D78" s="101"/>
-      <c r="E78" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F78" s="100">
+      <c r="D78" s="162"/>
+      <c r="E78" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F78" s="163">
         <v>46127</v>
       </c>
-      <c r="G78" s="102"/>
-      <c r="H78" s="98" t="s">
+      <c r="G78" s="164"/>
+      <c r="H78" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="I78" s="98" t="s">
+      <c r="I78" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="118" t="s">
+    <row r="79" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B79" s="120" t="s">
+      <c r="B79" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C79" s="113" t="str">
+      <c r="C79" s="161" t="str">
         <f>Sheet1!F89</f>
         <v>Tham mưu các vb triển khai đăng cai Hội Thi Tin học trẻ toàn quốc</v>
       </c>
-      <c r="D79" s="101"/>
-      <c r="E79" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F79" s="100">
+      <c r="D79" s="162"/>
+      <c r="E79" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F79" s="163">
         <v>46127</v>
       </c>
-      <c r="G79" s="102"/>
-      <c r="H79" s="98" t="s">
+      <c r="G79" s="164"/>
+      <c r="H79" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="I79" s="98" t="s">
+      <c r="I79" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A80" s="118" t="s">
+    <row r="80" spans="1:9" s="165" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A80" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B80" s="120" t="s">
+      <c r="B80" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C80" s="113" t="str">
+      <c r="C80" s="161" t="str">
         <f>Sheet1!F90</f>
         <v>Văn bản triển khai tuyên truyền tăng cường phòng chống, ngăn chặn bạo lực học đường</v>
       </c>
-      <c r="D80" s="101"/>
-      <c r="E80" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F80" s="100">
+      <c r="D80" s="162"/>
+      <c r="E80" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F80" s="163">
         <v>46127</v>
       </c>
-      <c r="G80" s="102"/>
-      <c r="H80" s="98" t="s">
+      <c r="G80" s="164"/>
+      <c r="H80" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="I80" s="98" t="s">
+      <c r="I80" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="118" t="s">
+    <row r="81" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B81" s="120" t="s">
+      <c r="B81" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C81" s="113" t="str">
+      <c r="C81" s="161" t="str">
         <f>Sheet1!F91</f>
         <v>Triển khai chương trình Hoa cúc trắng tháng 4</v>
       </c>
-      <c r="D81" s="101"/>
-      <c r="E81" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F81" s="100">
+      <c r="D81" s="162"/>
+      <c r="E81" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F81" s="163">
         <v>46132</v>
       </c>
-      <c r="G81" s="102"/>
-      <c r="H81" s="98" t="s">
+      <c r="G81" s="164"/>
+      <c r="H81" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="I81" s="98" t="s">
+      <c r="I81" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="118" t="s">
+    <row r="82" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B82" s="120" t="s">
+      <c r="B82" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C82" s="113" t="str">
+      <c r="C82" s="161" t="str">
         <f>Sheet1!F92</f>
         <v>Triển khai hướng nghiệp cho đội viên lớn</v>
       </c>
-      <c r="D82" s="101"/>
-      <c r="E82" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F82" s="100">
+      <c r="D82" s="162"/>
+      <c r="E82" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F82" s="163">
         <v>46116</v>
       </c>
-      <c r="G82" s="102"/>
-      <c r="H82" s="98" t="s">
+      <c r="G82" s="164"/>
+      <c r="H82" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="I82" s="98" t="s">
+      <c r="I82" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A83" s="118" t="s">
+    <row r="83" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B83" s="120" t="s">
+      <c r="B83" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C83" s="113" t="str">
+      <c r="C83" s="161" t="str">
         <f>Sheet1!F93</f>
         <v>Triển khai hội thi olympic tiếng anh trong cán bộ Đoàn, đoàn viên thanh niên</v>
       </c>
-      <c r="D83" s="101"/>
-      <c r="E83" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F83" s="100">
+      <c r="D83" s="162"/>
+      <c r="E83" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F83" s="163">
         <v>46127</v>
       </c>
-      <c r="G83" s="102"/>
-      <c r="H83" s="98" t="s">
+      <c r="G83" s="164"/>
+      <c r="H83" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="I83" s="98" t="s">
+      <c r="I83" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A84" s="118" t="s">
+    <row r="84" spans="1:9" s="165" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A84" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B84" s="120" t="s">
+      <c r="B84" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="113" t="str">
+      <c r="C84" s="161" t="str">
         <f>Sheet1!F94</f>
         <v>Kế hoạch triển khai các hoạt động phong trào Xây dựng tình bạn đẹp nói không với bạo lực học đường</v>
       </c>
-      <c r="D84" s="101"/>
-      <c r="E84" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F84" s="100">
+      <c r="D84" s="162"/>
+      <c r="E84" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F84" s="163">
         <v>46127</v>
       </c>
-      <c r="G84" s="102"/>
-      <c r="H84" s="98" t="s">
+      <c r="G84" s="164"/>
+      <c r="H84" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="I84" s="98" t="s">
+      <c r="I84" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A85" s="118" t="s">
+    <row r="85" spans="1:9" s="165" customFormat="1" ht="28" x14ac:dyDescent="0.2">
+      <c r="A85" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B85" s="120" t="s">
+      <c r="B85" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C85" s="113" t="str">
+      <c r="C85" s="161" t="str">
         <f>Sheet1!F95</f>
         <v>Tham mưu các điều kiện chuẩn bị tổ chức Hội thi Tin học trẻ tỉnh Lâm Đồng năm 2026</v>
       </c>
-      <c r="D85" s="101"/>
-      <c r="E85" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F85" s="100">
+      <c r="D85" s="162"/>
+      <c r="E85" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F85" s="163">
         <v>46142</v>
       </c>
-      <c r="G85" s="102"/>
-      <c r="H85" s="98" t="s">
+      <c r="G85" s="164"/>
+      <c r="H85" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="I85" s="98" t="s">
+      <c r="I85" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="118" t="s">
+    <row r="86" spans="1:9" s="165" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="B86" s="120" t="s">
+      <c r="B86" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="C86" s="113" t="str">
+      <c r="C86" s="161" t="str">
         <f>Sheet1!F96</f>
         <v xml:space="preserve">Triển khai cuộc thi Robotic cấp tỉnh </v>
       </c>
-      <c r="D86" s="101"/>
-      <c r="E86" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F86" s="100">
+      <c r="D86" s="162"/>
+      <c r="E86" s="163">
+        <v>46113</v>
+      </c>
+      <c r="F86" s="163">
         <v>46142</v>
       </c>
-      <c r="G86" s="102"/>
-      <c r="H86" s="98" t="s">
+      <c r="G86" s="164"/>
+      <c r="H86" s="78" t="s">
         <v>175</v>
       </c>
-      <c r="I86" s="98" t="s">
+      <c r="I86" s="78" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A87" s="118" t="s">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B87" s="98" t="s">
+      <c r="B87" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C87" s="113" t="str">
+      <c r="C87" s="77" t="str">
         <f>Sheet1!F97</f>
         <v>Tham mưu các nội dung quy trình thành lập Hội Sinh viên Việt Nam tỉnh</v>
       </c>
-      <c r="D87" s="101"/>
-      <c r="E87" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F87" s="100">
+      <c r="D87" s="66"/>
+      <c r="E87" s="65">
+        <v>46113</v>
+      </c>
+      <c r="F87" s="65">
         <v>46142</v>
       </c>
-      <c r="G87" s="102"/>
-      <c r="H87" s="98" t="s">
+      <c r="G87" s="67"/>
+      <c r="H87" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="I87" s="98" t="s">
+      <c r="I87" s="64" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="118" t="s">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="98" t="s">
+      <c r="B88" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="C88" s="113" t="str">
+      <c r="C88" s="77" t="str">
         <f>Sheet1!F98</f>
         <v>Đề án tổ chức Đại hội Hội</v>
       </c>
-      <c r="D88" s="101"/>
-      <c r="E88" s="100">
-        <v>46113</v>
-      </c>
-      <c r="F88" s="100">
+      <c r="D88" s="66"/>
+      <c r="E88" s="65">
+        <v>46113</v>
+      </c>
+      <c r="F88" s="65">
         <v>46142</v>
       </c>
-      <c r="G88" s="102"/>
-      <c r="H88" s="98" t="s">
+      <c r="G88" s="67"/>
+      <c r="H88" s="64" t="s">
         <v>175</v>
       </c>
-      <c r="I88" s="98" t="s">
+      <c r="I88" s="64" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3992,25 +4089,25 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$C$1:$C$3</xm:f>
           </x14:formula1>
           <xm:sqref>H89:I251</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$C$1:$C$30</xm:f>
           </x14:formula1>
           <xm:sqref>H2:I88</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$A$1:$A$3</xm:f>
           </x14:formula1>
           <xm:sqref>A2:A251</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list">
+        <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>DanhMuc!$B$1:$B$7</xm:f>
           </x14:formula1>
@@ -4023,2212 +4120,2212 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:J98"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" customWidth="1"/>
-    <col min="8" max="8" width="23.140625" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" style="130" customWidth="1"/>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
+    <col min="6" max="6" width="36.5" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" style="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="112"/>
+      <c r="D3" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="7" t="s">
+      <c r="E3" s="114"/>
+      <c r="F3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="121" t="s">
+      <c r="I3" s="81" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="B4" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="10"/>
-    </row>
-    <row r="5" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B5" s="11">
+      <c r="C4" s="116"/>
+      <c r="D4" s="116"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="116"/>
+      <c r="G4" s="116"/>
+      <c r="H4" s="116"/>
+      <c r="I4" s="117"/>
+    </row>
+    <row r="5" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B5" s="93">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="122">
+      <c r="I5" s="82">
         <v>46299</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="11"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14">
+    <row r="6" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B6" s="93"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="4">
         <v>2</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="17" t="s">
+      <c r="G6" s="120"/>
+      <c r="H6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I6" s="123">
+      <c r="I6" s="83">
         <v>46127</v>
       </c>
       <c r="J6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14">
+    <row r="7" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B7" s="93"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="4">
         <v>3</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="17" t="s">
+      <c r="G7" s="120"/>
+      <c r="H7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="122">
+      <c r="I7" s="82">
         <v>46122</v>
       </c>
       <c r="J7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="11"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14">
+    <row r="8" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B8" s="93"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="104"/>
+      <c r="E8" s="4">
         <v>4</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="17" t="s">
+      <c r="G8" s="120"/>
+      <c r="H8" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="122">
+      <c r="I8" s="82">
         <v>46122</v>
       </c>
       <c r="J8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="11"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14">
+    <row r="9" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B9" s="93"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="104"/>
+      <c r="E9" s="4">
         <v>5</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="17" t="s">
+      <c r="G9" s="120"/>
+      <c r="H9" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="122" t="s">
+      <c r="I9" s="82" t="s">
         <v>45</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14">
+    <row r="10" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B10" s="93"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="104"/>
+      <c r="E10" s="4">
         <v>6</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="17" t="s">
+      <c r="G10" s="120"/>
+      <c r="H10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="122" t="s">
+      <c r="I10" s="82" t="s">
         <v>48</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14">
+    <row r="11" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B11" s="93"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="104"/>
+      <c r="E11" s="4">
         <v>7</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="17" t="s">
+      <c r="G11" s="120"/>
+      <c r="H11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="82">
         <v>46127</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="11"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="14">
+    <row r="12" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B12" s="93"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="4">
         <v>9</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="22"/>
-      <c r="H12" s="17" t="s">
+      <c r="G12" s="121"/>
+      <c r="H12" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="122" t="s">
+      <c r="I12" s="82" t="s">
         <v>51</v>
       </c>
       <c r="J12">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
+    <row r="13" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B13" s="93"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="2"/>
-      <c r="E13" s="14">
+      <c r="E13" s="4">
         <v>10</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="17" t="s">
+      <c r="G13" s="8"/>
+      <c r="H13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="122">
+      <c r="I13" s="82">
         <v>46120</v>
       </c>
       <c r="J13">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13" t="s">
+    <row r="14" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B14" s="93"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="104" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="11">
         <v>1</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="122">
+      <c r="I14" s="82">
         <v>46132</v>
       </c>
       <c r="J14">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="24">
+    <row r="15" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B15" s="93"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="104"/>
+      <c r="E15" s="11">
         <v>2</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="26"/>
-      <c r="H15" s="17" t="s">
+      <c r="G15" s="123"/>
+      <c r="H15" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="122">
+      <c r="I15" s="82">
         <v>46132</v>
       </c>
       <c r="J15">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="24">
+    <row r="16" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B16" s="93"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="104"/>
+      <c r="E16" s="11">
         <v>3</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="26"/>
-      <c r="H16" s="17" t="s">
+      <c r="G16" s="123"/>
+      <c r="H16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I16" s="122">
+      <c r="I16" s="82">
         <v>46299</v>
       </c>
       <c r="J16">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="24">
+    <row r="17" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B17" s="93"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="11">
         <v>4</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="26"/>
-      <c r="H17" s="17" t="s">
+      <c r="G17" s="123"/>
+      <c r="H17" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="122">
+      <c r="I17" s="82">
         <v>46299</v>
       </c>
       <c r="J17">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="24">
+    <row r="18" spans="2:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="B18" s="93"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="104"/>
+      <c r="E18" s="11">
         <v>5</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="26"/>
-      <c r="H18" s="17" t="s">
+      <c r="G18" s="123"/>
+      <c r="H18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="122" t="s">
+      <c r="I18" s="82" t="s">
         <v>59</v>
       </c>
       <c r="J18">
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="24">
+    <row r="19" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B19" s="93"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="104"/>
+      <c r="E19" s="11">
         <v>6</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G19" s="26"/>
-      <c r="H19" s="17" t="s">
+      <c r="G19" s="123"/>
+      <c r="H19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I19" s="122" t="s">
+      <c r="I19" s="82" t="s">
         <v>59</v>
       </c>
       <c r="J19">
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="24">
+    <row r="20" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B20" s="93"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="104"/>
+      <c r="E20" s="11">
         <v>7</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="17" t="s">
+      <c r="G20" s="124"/>
+      <c r="H20" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="122" t="s">
+      <c r="I20" s="82" t="s">
         <v>59</v>
       </c>
       <c r="J20">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B21" s="11">
+    <row r="21" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B21" s="93">
         <v>2</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="13">
         <v>1</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="33" t="s">
+      <c r="H21" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="I21" s="124">
+      <c r="I21" s="84">
         <v>46132</v>
       </c>
       <c r="J21">
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B22" s="11"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="30">
+    <row r="22" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B22" s="93"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="98"/>
+      <c r="E22" s="13">
         <v>3</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I22" s="124" t="s">
+      <c r="I22" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J22">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B23" s="11"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="30">
+    <row r="23" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B23" s="93"/>
+      <c r="C23" s="95"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="13">
         <v>4</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I23" s="124" t="s">
+      <c r="I23" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J23">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B24" s="11"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="30">
+    <row r="24" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B24" s="93"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="98"/>
+      <c r="E24" s="13">
         <v>5</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I24" s="124" t="s">
+      <c r="I24" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J24">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B25" s="11"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="30">
+    <row r="25" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B25" s="93"/>
+      <c r="C25" s="95"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="13">
         <v>6</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="G25" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="36" t="s">
+      <c r="H25" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I25" s="124" t="s">
+      <c r="I25" s="84" t="s">
         <v>71</v>
       </c>
       <c r="J25">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B26" s="11"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="30">
+    <row r="26" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B26" s="93"/>
+      <c r="C26" s="95"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="13">
         <v>7</v>
       </c>
-      <c r="F26" s="31" t="s">
+      <c r="F26" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="G26" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="36" t="s">
+      <c r="H26" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I26" s="124">
+      <c r="I26" s="84">
         <v>46122</v>
       </c>
       <c r="J26">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="30">
+    <row r="27" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B27" s="93"/>
+      <c r="C27" s="95"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="13">
         <v>8</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="G27" s="35" t="s">
+      <c r="G27" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="36" t="s">
+      <c r="H27" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="I27" s="124">
+      <c r="I27" s="84">
         <v>46122</v>
       </c>
       <c r="J27">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="30">
+    <row r="28" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B28" s="93"/>
+      <c r="C28" s="95"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="13">
         <v>9</v>
       </c>
-      <c r="F28" s="31" t="s">
+      <c r="F28" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="G28" s="35" t="s">
+      <c r="G28" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="33" t="s">
+      <c r="H28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I28" s="124" t="s">
+      <c r="I28" s="84" t="s">
         <v>76</v>
       </c>
       <c r="J28">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="30">
+    <row r="29" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B29" s="93"/>
+      <c r="C29" s="95"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="13">
         <v>10</v>
       </c>
-      <c r="F29" s="31" t="s">
+      <c r="F29" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="33" t="s">
+      <c r="H29" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I29" s="124" t="s">
+      <c r="I29" s="84" t="s">
         <v>76</v>
       </c>
       <c r="J29">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B30" s="11"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="30">
+    <row r="30" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B30" s="93"/>
+      <c r="C30" s="95"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="13">
         <v>11</v>
       </c>
-      <c r="F30" s="31" t="s">
+      <c r="F30" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G30" s="35" t="s">
+      <c r="G30" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="36" t="s">
+      <c r="H30" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I30" s="124" t="s">
+      <c r="I30" s="84" t="s">
         <v>76</v>
       </c>
       <c r="J30">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="2:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="B31" s="11"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="30">
+    <row r="31" spans="2:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="B31" s="93"/>
+      <c r="C31" s="95"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="13">
         <v>12</v>
       </c>
-      <c r="F31" s="31" t="s">
+      <c r="F31" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="G31" s="37" t="s">
+      <c r="G31" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="38" t="s">
+      <c r="H31" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I31" s="124" t="s">
+      <c r="I31" s="84" t="s">
         <v>164</v>
       </c>
       <c r="J31">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="30">
+    <row r="32" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B32" s="93"/>
+      <c r="C32" s="95"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="13">
         <v>13</v>
       </c>
-      <c r="F32" s="39" t="s">
+      <c r="F32" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="G32" s="37" t="s">
+      <c r="G32" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="38" t="s">
+      <c r="H32" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I32" s="124" t="s">
+      <c r="I32" s="84" t="s">
         <v>164</v>
       </c>
       <c r="J32">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="30">
+    <row r="33" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B33" s="93"/>
+      <c r="C33" s="95"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="13">
         <v>14</v>
       </c>
-      <c r="F33" s="39" t="s">
+      <c r="F33" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="G33" s="37" t="s">
+      <c r="G33" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="H33" s="38" t="s">
+      <c r="H33" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="I33" s="124" t="s">
+      <c r="I33" s="84" t="s">
         <v>165</v>
       </c>
       <c r="J33">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B34" s="11"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="29" t="s">
+    <row r="34" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B34" s="93"/>
+      <c r="C34" s="95"/>
+      <c r="D34" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="13">
         <v>1</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="33" t="s">
+      <c r="H34" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I34" s="124" t="s">
+      <c r="I34" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J34">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="11"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="30">
+    <row r="35" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B35" s="93"/>
+      <c r="C35" s="95"/>
+      <c r="D35" s="98"/>
+      <c r="E35" s="13">
         <v>2</v>
       </c>
-      <c r="F35" s="31" t="s">
+      <c r="F35" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="33" t="s">
+      <c r="H35" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I35" s="124" t="s">
+      <c r="I35" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J35">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B36" s="11"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="30">
+    <row r="36" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B36" s="93"/>
+      <c r="C36" s="95"/>
+      <c r="D36" s="98"/>
+      <c r="E36" s="13">
         <v>3</v>
       </c>
-      <c r="F36" s="31" t="s">
+      <c r="F36" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="33" t="s">
+      <c r="H36" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I36" s="124" t="s">
+      <c r="I36" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J36">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B37" s="11"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="30">
+    <row r="37" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B37" s="93"/>
+      <c r="C37" s="95"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="13">
         <v>4</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="33" t="s">
+      <c r="H37" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="I37" s="124" t="s">
+      <c r="I37" s="84" t="s">
         <v>66</v>
       </c>
       <c r="J37">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="2:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="30">
+    <row r="38" spans="2:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="B38" s="93"/>
+      <c r="C38" s="95"/>
+      <c r="D38" s="98"/>
+      <c r="E38" s="13">
         <v>5</v>
       </c>
-      <c r="F38" s="41" t="s">
+      <c r="F38" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G38" s="35" t="s">
+      <c r="G38" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="36" t="s">
+      <c r="H38" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I38" s="124" t="s">
+      <c r="I38" s="84" t="s">
         <v>71</v>
       </c>
       <c r="J38">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="42" t="s">
+    <row r="39" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B39" s="93"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="98"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="35" t="s">
+      <c r="G39" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H39" s="36" t="s">
+      <c r="H39" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="I39" s="124" t="s">
+      <c r="I39" s="84" t="s">
         <v>88</v>
       </c>
       <c r="J39">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="30">
+    <row r="40" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B40" s="93"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="13">
         <v>6</v>
       </c>
-      <c r="F40" s="41" t="s">
+      <c r="F40" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="G40" s="35" t="s">
+      <c r="G40" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="H40" s="36" t="s">
+      <c r="H40" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I40" s="124" t="s">
+      <c r="I40" s="84" t="s">
         <v>71</v>
       </c>
       <c r="J40">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B41" s="44">
+    <row r="41" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B41" s="105">
         <v>3</v>
       </c>
-      <c r="C41" s="45" t="s">
+      <c r="C41" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="D41" s="46" t="s">
+      <c r="D41" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="47">
+      <c r="E41" s="25">
         <v>1</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="F41" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="49" t="s">
+      <c r="G41" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="50" t="s">
+      <c r="H41" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="I41" s="125" t="s">
+      <c r="I41" s="85" t="s">
         <v>166</v>
       </c>
       <c r="J41">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="47">
+    <row r="42" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B42" s="106"/>
+      <c r="C42" s="106"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="25">
         <v>2</v>
       </c>
-      <c r="F42" s="49" t="s">
+      <c r="F42" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="G42" s="49" t="s">
+      <c r="G42" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="H42" s="50" t="s">
+      <c r="H42" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="I42" s="125" t="s">
+      <c r="I42" s="85" t="s">
         <v>167</v>
       </c>
       <c r="J42">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="47">
+    <row r="43" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B43" s="106"/>
+      <c r="C43" s="106"/>
+      <c r="D43" s="109"/>
+      <c r="E43" s="25">
         <v>3</v>
       </c>
-      <c r="F43" s="49" t="s">
+      <c r="F43" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="G43" s="49" t="s">
+      <c r="G43" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="H43" s="50" t="s">
+      <c r="H43" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="I43" s="125" t="s">
+      <c r="I43" s="85" t="s">
         <v>168</v>
       </c>
       <c r="J43">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="47">
+    <row r="44" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B44" s="106"/>
+      <c r="C44" s="106"/>
+      <c r="D44" s="109"/>
+      <c r="E44" s="25">
         <v>4</v>
       </c>
-      <c r="F44" s="52" t="s">
+      <c r="F44" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="G44" s="53" t="s">
+      <c r="G44" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="H44" s="54" t="s">
+      <c r="H44" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="I44" s="124" t="s">
+      <c r="I44" s="84" t="s">
         <v>97</v>
       </c>
       <c r="J44">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="47">
+    <row r="45" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B45" s="106"/>
+      <c r="C45" s="106"/>
+      <c r="D45" s="109"/>
+      <c r="E45" s="25">
         <v>5</v>
       </c>
-      <c r="F45" s="55" t="s">
+      <c r="F45" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="G45" s="33" t="s">
+      <c r="G45" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H45" s="56" t="s">
+      <c r="H45" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="I45" s="124" t="s">
+      <c r="I45" s="84" t="s">
         <v>164</v>
       </c>
       <c r="J45">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B46" s="45"/>
-      <c r="C46" s="45"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="47">
+    <row r="46" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B46" s="106"/>
+      <c r="C46" s="106"/>
+      <c r="D46" s="109"/>
+      <c r="E46" s="25">
         <v>6</v>
       </c>
-      <c r="F46" s="31" t="s">
+      <c r="F46" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="G46" s="33" t="s">
+      <c r="G46" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="56" t="s">
+      <c r="H46" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="I46" s="124" t="s">
+      <c r="I46" s="84" t="s">
         <v>97</v>
       </c>
       <c r="J46">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="2:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="47">
+    <row r="47" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B47" s="106"/>
+      <c r="C47" s="106"/>
+      <c r="D47" s="109"/>
+      <c r="E47" s="25">
         <v>7</v>
       </c>
-      <c r="F47" s="57" t="s">
+      <c r="F47" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="G47" s="33" t="s">
+      <c r="G47" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="56" t="s">
+      <c r="H47" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="I47" s="124" t="s">
+      <c r="I47" s="84" t="s">
         <v>164</v>
       </c>
       <c r="J47">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="47">
+    <row r="48" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B48" s="106"/>
+      <c r="C48" s="106"/>
+      <c r="D48" s="110"/>
+      <c r="E48" s="25">
         <v>8</v>
       </c>
-      <c r="F48" s="49" t="s">
+      <c r="F48" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="G48" s="33" t="s">
+      <c r="G48" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H48" s="36" t="s">
+      <c r="H48" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="I48" s="126" t="s">
+      <c r="I48" s="86" t="s">
         <v>164</v>
       </c>
       <c r="J48">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="29" t="s">
+    <row r="49" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B49" s="106"/>
+      <c r="C49" s="106"/>
+      <c r="D49" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="59">
+      <c r="E49" s="35">
         <v>1</v>
       </c>
-      <c r="F49" s="60" t="s">
+      <c r="F49" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="G49" s="33" t="s">
+      <c r="G49" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H49" s="36" t="s">
+      <c r="H49" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="I49" s="127" t="s">
+      <c r="I49" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J49">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="59">
+    <row r="50" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B50" s="106"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="98"/>
+      <c r="E50" s="35">
         <v>2</v>
       </c>
-      <c r="F50" s="31" t="s">
+      <c r="F50" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="G50" s="33" t="s">
+      <c r="G50" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H50" s="33" t="s">
+      <c r="H50" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I50" s="127" t="s">
+      <c r="I50" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J50">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="34"/>
-      <c r="E51" s="59">
+    <row r="51" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B51" s="106"/>
+      <c r="C51" s="106"/>
+      <c r="D51" s="98"/>
+      <c r="E51" s="35">
         <v>3</v>
       </c>
-      <c r="F51" s="61" t="s">
+      <c r="F51" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="G51" s="36" t="s">
+      <c r="G51" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H51" s="36" t="s">
+      <c r="H51" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I51" s="127" t="s">
+      <c r="I51" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J51">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="34"/>
-      <c r="E52" s="59">
+    <row r="52" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B52" s="106"/>
+      <c r="C52" s="106"/>
+      <c r="D52" s="98"/>
+      <c r="E52" s="35">
         <v>4</v>
       </c>
-      <c r="F52" s="61" t="s">
+      <c r="F52" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="G52" s="36" t="s">
+      <c r="G52" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H52" s="36" t="s">
+      <c r="H52" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I52" s="127" t="s">
+      <c r="I52" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J52">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="59">
+    <row r="53" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B53" s="106"/>
+      <c r="C53" s="106"/>
+      <c r="D53" s="98"/>
+      <c r="E53" s="35">
         <v>5</v>
       </c>
-      <c r="F53" s="55" t="s">
+      <c r="F53" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="G53" s="36" t="s">
+      <c r="G53" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H53" s="36" t="s">
+      <c r="H53" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="I53" s="127" t="s">
+      <c r="I53" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J53">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="34"/>
-      <c r="E54" s="59">
+    <row r="54" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B54" s="106"/>
+      <c r="C54" s="106"/>
+      <c r="D54" s="98"/>
+      <c r="E54" s="35">
         <v>6</v>
       </c>
-      <c r="F54" s="31" t="s">
+      <c r="F54" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="G54" s="33" t="s">
+      <c r="G54" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H54" s="36" t="s">
+      <c r="H54" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="I54" s="127" t="s">
+      <c r="I54" s="87" t="s">
         <v>109</v>
       </c>
       <c r="J54">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="34"/>
-      <c r="E55" s="59">
+    <row r="55" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B55" s="106"/>
+      <c r="C55" s="106"/>
+      <c r="D55" s="98"/>
+      <c r="E55" s="35">
         <v>7</v>
       </c>
-      <c r="F55" s="31" t="s">
+      <c r="F55" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="G55" s="33" t="s">
+      <c r="G55" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H55" s="36" t="s">
+      <c r="H55" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="I55" s="127" t="s">
+      <c r="I55" s="87" t="s">
         <v>97</v>
       </c>
       <c r="J55">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="59">
+    <row r="56" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B56" s="106"/>
+      <c r="C56" s="106"/>
+      <c r="D56" s="98"/>
+      <c r="E56" s="35">
         <v>8</v>
       </c>
-      <c r="F56" s="62" t="s">
+      <c r="F56" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="G56" s="62" t="s">
+      <c r="G56" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="H56" s="53" t="s">
+      <c r="H56" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="I56" s="127" t="s">
+      <c r="I56" s="87" t="s">
         <v>112</v>
       </c>
       <c r="J56">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="59">
+    <row r="57" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B57" s="106"/>
+      <c r="C57" s="106"/>
+      <c r="D57" s="98"/>
+      <c r="E57" s="35">
         <v>9</v>
       </c>
-      <c r="F57" s="49" t="s">
+      <c r="F57" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="G57" s="49" t="s">
+      <c r="G57" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="H57" s="36" t="s">
+      <c r="H57" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="I57" s="127" t="s">
+      <c r="I57" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J57">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B58" s="63"/>
-      <c r="C58" s="63"/>
-      <c r="D58" s="40"/>
-      <c r="E58" s="59">
+    <row r="58" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B58" s="107"/>
+      <c r="C58" s="107"/>
+      <c r="D58" s="99"/>
+      <c r="E58" s="35">
         <v>10</v>
       </c>
-      <c r="F58" s="49" t="s">
+      <c r="F58" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="G58" s="49" t="s">
+      <c r="G58" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="H58" s="36" t="s">
+      <c r="H58" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="I58" s="127" t="s">
+      <c r="I58" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J58">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="64" t="s">
+    <row r="59" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="B59" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="64"/>
-      <c r="D59" s="64"/>
-      <c r="E59" s="64"/>
-      <c r="F59" s="64"/>
-      <c r="G59" s="64"/>
-      <c r="H59" s="64"/>
-      <c r="I59" s="64"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="100"/>
+      <c r="E59" s="100"/>
+      <c r="F59" s="100"/>
+      <c r="G59" s="100"/>
+      <c r="H59" s="100"/>
+      <c r="I59" s="100"/>
       <c r="J59">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B60" s="65">
+    <row r="60" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B60" s="101">
         <v>1</v>
       </c>
-      <c r="C60" s="66" t="s">
+      <c r="C60" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="E60" s="67">
+      <c r="E60" s="39">
         <v>1</v>
       </c>
-      <c r="F60" s="68" t="s">
+      <c r="F60" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="G60" s="35" t="s">
+      <c r="G60" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H60" s="36" t="s">
+      <c r="H60" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I60" s="127">
+      <c r="I60" s="87">
         <v>46127</v>
       </c>
       <c r="J60">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B61" s="69"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="70">
+    <row r="61" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B61" s="102"/>
+      <c r="C61" s="95"/>
+      <c r="D61" s="104"/>
+      <c r="E61" s="42">
         <v>2</v>
       </c>
-      <c r="F61" s="68" t="s">
+      <c r="F61" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="G61" s="35" t="s">
+      <c r="G61" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H61" s="36" t="s">
+      <c r="H61" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I61" s="127">
+      <c r="I61" s="87">
         <v>46122</v>
       </c>
       <c r="J61">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B62" s="69"/>
-      <c r="C62" s="28"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="67">
+    <row r="62" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B62" s="102"/>
+      <c r="C62" s="95"/>
+      <c r="D62" s="104"/>
+      <c r="E62" s="39">
         <v>3</v>
       </c>
-      <c r="F62" s="68" t="s">
+      <c r="F62" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="G62" s="35" t="s">
+      <c r="G62" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H62" s="36" t="s">
+      <c r="H62" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I62" s="127">
+      <c r="I62" s="87">
         <v>46118</v>
       </c>
       <c r="J62">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B63" s="69"/>
-      <c r="C63" s="28"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="67">
+    <row r="63" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B63" s="102"/>
+      <c r="C63" s="95"/>
+      <c r="D63" s="104"/>
+      <c r="E63" s="39">
         <v>4</v>
       </c>
-      <c r="F63" s="68" t="s">
+      <c r="F63" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="G63" s="35" t="s">
+      <c r="G63" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H63" s="36" t="s">
+      <c r="H63" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I63" s="127">
+      <c r="I63" s="87">
         <v>46140</v>
       </c>
       <c r="J63">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B64" s="69"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="67">
+    <row r="64" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B64" s="102"/>
+      <c r="C64" s="95"/>
+      <c r="D64" s="104"/>
+      <c r="E64" s="39">
         <v>5</v>
       </c>
-      <c r="F64" s="71" t="s">
+      <c r="F64" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="G64" s="35" t="s">
+      <c r="G64" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H64" s="36" t="s">
+      <c r="H64" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I64" s="127">
+      <c r="I64" s="87">
         <v>46141</v>
       </c>
       <c r="J64">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B65" s="69"/>
-      <c r="C65" s="28"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="70">
+    <row r="65" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B65" s="102"/>
+      <c r="C65" s="95"/>
+      <c r="D65" s="104"/>
+      <c r="E65" s="42">
         <v>6</v>
       </c>
-      <c r="F65" s="71" t="s">
+      <c r="F65" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="G65" s="35" t="s">
+      <c r="G65" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H65" s="36" t="s">
+      <c r="H65" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I65" s="127">
+      <c r="I65" s="87">
         <v>46141</v>
       </c>
       <c r="J65">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="2:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="69"/>
-      <c r="C66" s="28"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="67">
+    <row r="66" spans="2:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="B66" s="102"/>
+      <c r="C66" s="95"/>
+      <c r="D66" s="104"/>
+      <c r="E66" s="39">
         <v>7</v>
       </c>
-      <c r="F66" s="68" t="s">
+      <c r="F66" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="G66" s="35" t="s">
+      <c r="G66" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H66" s="36" t="s">
+      <c r="H66" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I66" s="127">
+      <c r="I66" s="87">
         <v>46140</v>
       </c>
       <c r="J66">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B67" s="69"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="67">
+    <row r="67" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B67" s="102"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="104"/>
+      <c r="E67" s="39">
         <v>8</v>
       </c>
-      <c r="F67" s="72" t="s">
+      <c r="F67" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="G67" s="36" t="s">
+      <c r="G67" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="H67" s="36" t="s">
+      <c r="H67" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I67" s="127">
+      <c r="I67" s="87">
         <v>46127</v>
       </c>
       <c r="J67">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B68" s="69"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="67">
+    <row r="68" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B68" s="102"/>
+      <c r="C68" s="95"/>
+      <c r="D68" s="104"/>
+      <c r="E68" s="39">
         <v>9</v>
       </c>
-      <c r="F68" s="68" t="s">
+      <c r="F68" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="G68" s="35" t="s">
+      <c r="G68" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H68" s="36" t="s">
+      <c r="H68" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I68" s="127">
+      <c r="I68" s="87">
         <v>46136</v>
       </c>
       <c r="J68">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B69" s="69"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="70">
+    <row r="69" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B69" s="102"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="104"/>
+      <c r="E69" s="42">
         <v>10</v>
       </c>
-      <c r="F69" s="68" t="s">
+      <c r="F69" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="G69" s="35" t="s">
+      <c r="G69" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H69" s="36" t="s">
+      <c r="H69" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I69" s="127">
+      <c r="I69" s="87">
         <v>46115</v>
       </c>
       <c r="J69">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B70" s="69"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="67">
+    <row r="70" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B70" s="102"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="104"/>
+      <c r="E70" s="39">
         <v>11</v>
       </c>
-      <c r="F70" s="68" t="s">
+      <c r="F70" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="G70" s="35" t="s">
+      <c r="G70" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H70" s="36" t="s">
+      <c r="H70" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I70" s="127">
+      <c r="I70" s="87">
         <v>46119</v>
       </c>
       <c r="J70">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B71" s="69"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="67">
+    <row r="71" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B71" s="102"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="104"/>
+      <c r="E71" s="39">
         <v>12</v>
       </c>
-      <c r="F71" s="68" t="s">
+      <c r="F71" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="G71" s="35" t="s">
+      <c r="G71" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H71" s="36" t="s">
+      <c r="H71" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I71" s="127">
+      <c r="I71" s="87">
         <v>46136</v>
       </c>
       <c r="J71">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B72" s="69"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="29" t="s">
+    <row r="72" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B72" s="102"/>
+      <c r="C72" s="95"/>
+      <c r="D72" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E72" s="67">
+      <c r="E72" s="39">
         <v>1</v>
       </c>
-      <c r="F72" s="68" t="s">
+      <c r="F72" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="G72" s="73" t="s">
+      <c r="G72" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="H72" s="74" t="s">
+      <c r="H72" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="I72" s="127" t="s">
+      <c r="I72" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J72">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="69"/>
-      <c r="C73" s="28"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="67">
+    <row r="73" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B73" s="102"/>
+      <c r="C73" s="95"/>
+      <c r="D73" s="98"/>
+      <c r="E73" s="39">
         <v>2</v>
       </c>
-      <c r="F73" s="68" t="s">
+      <c r="F73" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="G73" s="35" t="s">
+      <c r="G73" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H73" s="36" t="s">
+      <c r="H73" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I73" s="127" t="s">
+      <c r="I73" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J73">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B74" s="69"/>
-      <c r="C74" s="28"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="67">
+    <row r="74" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B74" s="102"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="98"/>
+      <c r="E74" s="39">
         <v>3</v>
       </c>
-      <c r="F74" s="68" t="s">
+      <c r="F74" s="40" t="s">
         <v>133</v>
       </c>
-      <c r="G74" s="35" t="s">
+      <c r="G74" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H74" s="36" t="s">
+      <c r="H74" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I74" s="127" t="s">
+      <c r="I74" s="87" t="s">
         <v>71</v>
       </c>
       <c r="J74">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B75" s="69"/>
-      <c r="C75" s="28"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="67">
+    <row r="75" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B75" s="102"/>
+      <c r="C75" s="95"/>
+      <c r="D75" s="98"/>
+      <c r="E75" s="39">
         <v>4</v>
       </c>
-      <c r="F75" s="75" t="s">
+      <c r="F75" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="G75" s="35" t="s">
+      <c r="G75" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H75" s="36" t="s">
+      <c r="H75" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I75" s="127">
+      <c r="I75" s="87">
         <v>46114</v>
       </c>
       <c r="J75">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B76" s="76"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="34"/>
-      <c r="E76" s="67">
+    <row r="76" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B76" s="103"/>
+      <c r="C76" s="95"/>
+      <c r="D76" s="98"/>
+      <c r="E76" s="39">
         <v>5</v>
       </c>
-      <c r="F76" s="68" t="s">
+      <c r="F76" s="40" t="s">
         <v>135</v>
       </c>
-      <c r="G76" s="35" t="s">
+      <c r="G76" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H76" s="36" t="s">
+      <c r="H76" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I76" s="127">
+      <c r="I76" s="87">
         <v>46125</v>
       </c>
       <c r="J76">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="2:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B77" s="77"/>
-      <c r="C77" s="43"/>
-      <c r="D77" s="40"/>
-      <c r="E77" s="67">
+    <row r="77" spans="2:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="B77" s="41"/>
+      <c r="C77" s="96"/>
+      <c r="D77" s="99"/>
+      <c r="E77" s="39">
         <v>6</v>
       </c>
-      <c r="F77" s="72" t="s">
+      <c r="F77" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="G77" s="73" t="s">
+      <c r="G77" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="H77" s="36" t="s">
+      <c r="H77" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="I77" s="127">
+      <c r="I77" s="87">
         <v>46141</v>
       </c>
       <c r="J77">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="2:10" ht="63" x14ac:dyDescent="0.25">
-      <c r="B78" s="65">
+    <row r="78" spans="2:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="B78" s="101">
         <v>2</v>
       </c>
-      <c r="C78" s="66" t="s">
+      <c r="C78" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="D78" s="29" t="s">
+      <c r="D78" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="E78" s="67">
+      <c r="E78" s="39">
         <v>1</v>
       </c>
-      <c r="F78" s="78" t="s">
+      <c r="F78" s="48" t="s">
         <v>138</v>
       </c>
-      <c r="G78" s="73" t="s">
+      <c r="G78" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="H78" s="36" t="s">
+      <c r="H78" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I78" s="127">
+      <c r="I78" s="87">
         <v>46132</v>
       </c>
       <c r="J78">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="2:10" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="B79" s="69"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="67">
+    <row r="79" spans="2:10" ht="85" x14ac:dyDescent="0.2">
+      <c r="B79" s="102"/>
+      <c r="C79" s="95"/>
+      <c r="D79" s="98"/>
+      <c r="E79" s="39">
         <v>2</v>
       </c>
-      <c r="F79" s="79" t="s">
+      <c r="F79" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="G79" s="73" t="s">
+      <c r="G79" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="H79" s="36" t="s">
+      <c r="H79" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I79" s="127">
+      <c r="I79" s="87">
         <v>46141</v>
       </c>
       <c r="J79">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B80" s="69"/>
-      <c r="C80" s="28"/>
-      <c r="D80" s="29" t="s">
+    <row r="80" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B80" s="102"/>
+      <c r="C80" s="95"/>
+      <c r="D80" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E80" s="67">
+      <c r="E80" s="39">
         <v>1</v>
       </c>
-      <c r="F80" s="68" t="s">
+      <c r="F80" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="G80" s="35" t="s">
+      <c r="G80" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="H80" s="36" t="s">
+      <c r="H80" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I80" s="127" t="s">
+      <c r="I80" s="87" t="s">
         <v>97</v>
       </c>
       <c r="J80">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B81" s="69"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="67">
+    <row r="81" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B81" s="102"/>
+      <c r="C81" s="95"/>
+      <c r="D81" s="98"/>
+      <c r="E81" s="39">
         <v>2</v>
       </c>
-      <c r="F81" s="80" t="s">
+      <c r="F81" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="G81" s="73" t="s">
+      <c r="G81" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="H81" s="74" t="s">
+      <c r="H81" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="I81" s="127" t="s">
+      <c r="I81" s="87" t="s">
         <v>97</v>
       </c>
       <c r="J81">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B82" s="69"/>
-      <c r="C82" s="28"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="81">
+    <row r="82" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B82" s="102"/>
+      <c r="C82" s="95"/>
+      <c r="D82" s="98"/>
+      <c r="E82" s="51">
         <v>3</v>
       </c>
-      <c r="F82" s="82" t="s">
+      <c r="F82" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="G82" s="83" t="s">
+      <c r="G82" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="H82" s="84" t="s">
+      <c r="H82" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="I82" s="128" t="s">
+      <c r="I82" s="88" t="s">
         <v>71</v>
       </c>
       <c r="J82">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B83" s="77"/>
-      <c r="C83" s="85"/>
-      <c r="D83" s="86"/>
-      <c r="E83" s="87">
+    <row r="83" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B83" s="41"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="17"/>
+      <c r="E83" s="55">
         <v>4</v>
       </c>
-      <c r="F83" s="57" t="s">
+      <c r="F83" s="34" t="s">
         <v>143</v>
       </c>
-      <c r="G83" s="83" t="s">
+      <c r="G83" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="H83" s="36" t="s">
+      <c r="H83" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="I83" s="124" t="s">
+      <c r="I83" s="84" t="s">
         <v>144</v>
       </c>
       <c r="J83">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B84" s="88" t="s">
+    <row r="84" spans="2:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="B84" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="C84" s="88"/>
-      <c r="D84" s="88"/>
-      <c r="E84" s="88"/>
-      <c r="F84" s="88"/>
-      <c r="G84" s="88"/>
-      <c r="H84" s="88"/>
-      <c r="I84" s="88"/>
+      <c r="C84" s="92"/>
+      <c r="D84" s="92"/>
+      <c r="E84" s="92"/>
+      <c r="F84" s="92"/>
+      <c r="G84" s="92"/>
+      <c r="H84" s="92"/>
+      <c r="I84" s="92"/>
       <c r="J84">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B85" s="11">
+    <row r="85" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B85" s="93">
         <v>1</v>
       </c>
-      <c r="C85" s="66" t="s">
+      <c r="C85" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="D85" s="29" t="s">
+      <c r="D85" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="E85" s="70">
+      <c r="E85" s="42">
         <v>1</v>
       </c>
-      <c r="F85" s="61" t="s">
+      <c r="F85" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="G85" s="36" t="s">
+      <c r="G85" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H85" s="36" t="s">
+      <c r="H85" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="I85" s="127">
+      <c r="I85" s="87">
         <v>46085</v>
       </c>
       <c r="J85">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B86" s="11"/>
-      <c r="C86" s="28"/>
-      <c r="D86" s="34"/>
-      <c r="E86" s="70">
+    <row r="86" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B86" s="93"/>
+      <c r="C86" s="95"/>
+      <c r="D86" s="98"/>
+      <c r="E86" s="42">
         <v>2</v>
       </c>
-      <c r="F86" s="61" t="s">
+      <c r="F86" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="G86" s="36" t="s">
+      <c r="G86" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H86" s="36" t="s">
+      <c r="H86" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="I86" s="127">
+      <c r="I86" s="87">
         <v>46299</v>
       </c>
       <c r="J86">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="2:10" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="B87" s="11"/>
-      <c r="C87" s="28"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="70">
+    <row r="87" spans="2:10" ht="68" x14ac:dyDescent="0.2">
+      <c r="B87" s="93"/>
+      <c r="C87" s="95"/>
+      <c r="D87" s="98"/>
+      <c r="E87" s="42">
         <v>3</v>
       </c>
-      <c r="F87" s="61" t="s">
+      <c r="F87" s="37" t="s">
         <v>149</v>
       </c>
-      <c r="G87" s="36" t="s">
+      <c r="G87" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H87" s="36" t="s">
+      <c r="H87" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="I87" s="127" t="s">
+      <c r="I87" s="87" t="s">
         <v>169</v>
       </c>
       <c r="J87">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B88" s="11"/>
-      <c r="C88" s="28"/>
-      <c r="D88" s="34"/>
-      <c r="E88" s="70">
+    <row r="88" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B88" s="93"/>
+      <c r="C88" s="95"/>
+      <c r="D88" s="98"/>
+      <c r="E88" s="42">
         <v>4</v>
       </c>
-      <c r="F88" s="78" t="s">
+      <c r="F88" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="G88" s="36" t="s">
+      <c r="G88" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H88" s="36" t="s">
+      <c r="H88" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="I88" s="127" t="s">
+      <c r="I88" s="87" t="s">
         <v>165</v>
       </c>
       <c r="J88">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B89" s="11"/>
-      <c r="C89" s="28"/>
-      <c r="D89" s="34"/>
-      <c r="E89" s="70"/>
-      <c r="F89" s="78" t="s">
+    <row r="89" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B89" s="93"/>
+      <c r="C89" s="95"/>
+      <c r="D89" s="98"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="G89" s="36" t="s">
+      <c r="G89" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H89" s="36" t="s">
+      <c r="H89" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I89" s="127">
+      <c r="I89" s="87">
         <v>46299</v>
       </c>
       <c r="J89">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B90" s="11"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="40"/>
-      <c r="E90" s="70">
+    <row r="90" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B90" s="93"/>
+      <c r="C90" s="95"/>
+      <c r="D90" s="99"/>
+      <c r="E90" s="42">
         <v>5</v>
       </c>
-      <c r="F90" s="78" t="s">
+      <c r="F90" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="G90" s="36" t="s">
+      <c r="G90" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H90" s="36" t="s">
+      <c r="H90" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I90" s="127" t="s">
+      <c r="I90" s="87" t="s">
         <v>165</v>
       </c>
       <c r="J90">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B91" s="11"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="29" t="s">
+    <row r="91" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B91" s="93"/>
+      <c r="C91" s="95"/>
+      <c r="D91" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="E91" s="70">
+      <c r="E91" s="42">
         <v>6</v>
       </c>
-      <c r="F91" s="61" t="s">
+      <c r="F91" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="G91" s="36" t="s">
+      <c r="G91" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H91" s="36" t="s">
+      <c r="H91" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="I91" s="127" t="s">
+      <c r="I91" s="87" t="s">
         <v>164</v>
       </c>
       <c r="J91">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B92" s="11"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="34"/>
-      <c r="E92" s="70">
+    <row r="92" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B92" s="93"/>
+      <c r="C92" s="95"/>
+      <c r="D92" s="98"/>
+      <c r="E92" s="42">
         <v>7</v>
       </c>
-      <c r="F92" s="61" t="s">
+      <c r="F92" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="G92" s="36" t="s">
+      <c r="G92" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H92" s="36" t="s">
+      <c r="H92" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="I92" s="127">
+      <c r="I92" s="87">
         <v>46146</v>
       </c>
       <c r="J92">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B93" s="11"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="34"/>
-      <c r="E93" s="70">
+    <row r="93" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B93" s="93"/>
+      <c r="C93" s="95"/>
+      <c r="D93" s="98"/>
+      <c r="E93" s="42">
         <v>8</v>
       </c>
-      <c r="F93" s="78" t="s">
+      <c r="F93" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="G93" s="36" t="s">
+      <c r="G93" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H93" s="36" t="s">
+      <c r="H93" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="I93" s="127">
+      <c r="I93" s="87">
         <v>46146</v>
       </c>
       <c r="J93">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B94" s="11"/>
-      <c r="C94" s="28"/>
-      <c r="D94" s="34"/>
-      <c r="E94" s="70">
+    <row r="94" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B94" s="93"/>
+      <c r="C94" s="95"/>
+      <c r="D94" s="98"/>
+      <c r="E94" s="42">
         <v>9</v>
       </c>
-      <c r="F94" s="61" t="s">
+      <c r="F94" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="G94" s="36" t="s">
+      <c r="G94" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H94" s="36" t="s">
+      <c r="H94" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="I94" s="127">
+      <c r="I94" s="87">
         <v>46299</v>
       </c>
       <c r="J94">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="2:10" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="B95" s="11"/>
-      <c r="C95" s="28"/>
-      <c r="D95" s="34"/>
-      <c r="E95" s="70">
+    <row r="95" spans="2:10" ht="51" x14ac:dyDescent="0.2">
+      <c r="B95" s="93"/>
+      <c r="C95" s="95"/>
+      <c r="D95" s="98"/>
+      <c r="E95" s="42">
         <v>10</v>
       </c>
-      <c r="F95" s="89" t="s">
+      <c r="F95" s="56" t="s">
         <v>159</v>
       </c>
-      <c r="G95" s="36" t="s">
+      <c r="G95" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="H95" s="36" t="s">
+      <c r="H95" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I95" s="127">
+      <c r="I95" s="87">
         <v>46142</v>
       </c>
       <c r="J95">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B96" s="11"/>
-      <c r="C96" s="43"/>
-      <c r="D96" s="40"/>
-      <c r="E96" s="90">
+    <row r="96" spans="2:10" ht="17" x14ac:dyDescent="0.2">
+      <c r="B96" s="93"/>
+      <c r="C96" s="96"/>
+      <c r="D96" s="99"/>
+      <c r="E96" s="57">
         <v>11</v>
       </c>
-      <c r="F96" s="55" t="s">
+      <c r="F96" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="G96" s="81" t="s">
+      <c r="G96" s="51" t="s">
         <v>146</v>
       </c>
-      <c r="H96" s="38" t="s">
+      <c r="H96" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="I96" s="128">
+      <c r="I96" s="88">
         <v>46142</v>
       </c>
       <c r="J96">
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B97" s="11">
+    <row r="97" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B97" s="93">
         <v>2</v>
       </c>
-      <c r="C97" s="28" t="s">
+      <c r="C97" s="95" t="s">
         <v>161</v>
       </c>
-      <c r="D97" s="29" t="s">
+      <c r="D97" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="E97" s="32">
+      <c r="E97" s="15">
         <v>1</v>
       </c>
-      <c r="F97" s="91" t="s">
+      <c r="F97" s="58" t="s">
         <v>162</v>
       </c>
-      <c r="G97" s="92" t="s">
+      <c r="G97" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="H97" s="53" t="s">
+      <c r="H97" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="I97" s="129" t="s">
+      <c r="I97" s="89" t="s">
         <v>97</v>
       </c>
       <c r="J97">
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="2:10" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B98" s="11"/>
-      <c r="C98" s="43"/>
-      <c r="D98" s="40"/>
-      <c r="E98" s="93">
+    <row r="98" spans="2:10" ht="34" x14ac:dyDescent="0.2">
+      <c r="B98" s="93"/>
+      <c r="C98" s="96"/>
+      <c r="D98" s="99"/>
+      <c r="E98" s="60">
         <v>2</v>
       </c>
-      <c r="F98" s="61" t="s">
+      <c r="F98" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="G98" s="36" t="s">
+      <c r="G98" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="H98" s="36" t="s">
+      <c r="H98" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="I98" s="127">
+      <c r="I98" s="87">
         <v>46086</v>
       </c>
       <c r="J98">
@@ -6237,11 +6334,23 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B84:I84"/>
-    <mergeCell ref="B85:B96"/>
-    <mergeCell ref="C85:C96"/>
-    <mergeCell ref="D85:D90"/>
-    <mergeCell ref="D91:D96"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="B5:B20"/>
+    <mergeCell ref="C5:C20"/>
+    <mergeCell ref="D5:D12"/>
+    <mergeCell ref="G5:G12"/>
+    <mergeCell ref="D14:D20"/>
+    <mergeCell ref="G14:G20"/>
+    <mergeCell ref="B21:B40"/>
+    <mergeCell ref="C21:C40"/>
+    <mergeCell ref="D21:D33"/>
+    <mergeCell ref="D34:D40"/>
+    <mergeCell ref="B41:B58"/>
+    <mergeCell ref="C41:C58"/>
+    <mergeCell ref="D41:D48"/>
+    <mergeCell ref="D49:D58"/>
     <mergeCell ref="B97:B98"/>
     <mergeCell ref="C97:C98"/>
     <mergeCell ref="D97:D98"/>
@@ -6254,40 +6363,28 @@
     <mergeCell ref="C78:C82"/>
     <mergeCell ref="D78:D79"/>
     <mergeCell ref="D80:D82"/>
-    <mergeCell ref="B21:B40"/>
-    <mergeCell ref="C21:C40"/>
-    <mergeCell ref="D21:D33"/>
-    <mergeCell ref="D34:D40"/>
-    <mergeCell ref="B41:B58"/>
-    <mergeCell ref="C41:C58"/>
-    <mergeCell ref="D41:D48"/>
-    <mergeCell ref="D49:D58"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:B20"/>
-    <mergeCell ref="C5:C20"/>
-    <mergeCell ref="D5:D12"/>
-    <mergeCell ref="G5:G12"/>
-    <mergeCell ref="D14:D20"/>
-    <mergeCell ref="G14:G20"/>
+    <mergeCell ref="B84:I84"/>
+    <mergeCell ref="B85:B96"/>
+    <mergeCell ref="C85:C96"/>
+    <mergeCell ref="D85:D90"/>
+    <mergeCell ref="D91:D96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="47.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="47.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="1"/>
+    <col min="3" max="3" width="30.6640625" style="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -6301,7 +6398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -6315,7 +6412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -6329,7 +6426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -6340,7 +6437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -6351,7 +6448,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -6362,7 +6459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
@@ -6373,7 +6470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
@@ -6381,7 +6478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>22</v>
       </c>
@@ -6389,7 +6486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>170</v>
       </c>
@@ -6397,7 +6494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>171</v>
       </c>
@@ -6405,7 +6502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>172</v>
       </c>
@@ -6413,7 +6510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>173</v>
       </c>
@@ -6421,7 +6518,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>174</v>
       </c>
@@ -6429,7 +6526,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>175</v>
       </c>
@@ -6437,7 +6534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="C16" s="1" t="s">
         <v>176</v>
       </c>
@@ -6445,7 +6542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>28</v>
       </c>
@@ -6453,7 +6550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>177</v>
       </c>
@@ -6461,7 +6558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>178</v>
       </c>
@@ -6469,7 +6566,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>179</v>
       </c>
@@ -6477,7 +6574,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>180</v>
       </c>
